--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -567,7 +567,7 @@
         <v>45097</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>45371</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>44817</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45957.47775462963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45183</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>44890</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45930</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>44840</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>46002</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>46100.35730324074</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45203</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44376</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>44545</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45599</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45583</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44819</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44440</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>44643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45520.59846064815</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>45713.26855324074</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>45819.50840277778</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45840.448125</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44572.64711805555</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45763.38111111111</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45477.48292824074</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45357.50277777778</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45048</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45035</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>44834</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44462</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>44747</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44454</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44740</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>44830</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45589.63901620371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>45352</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>45904.45417824074</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45791.6516550926</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45555.45984953704</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45240</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45342</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45930</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45586.49113425926</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>46069.34824074074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45835.35682870371</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>45239</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45713</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44998</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44880</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>44908</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>45148.4965162037</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45419.45423611111</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45085</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45408.38405092592</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44819</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45009.32462962963</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>44434</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>45891.48929398148</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>46141.63559027778</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>45261</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>46166.69366898148</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45400</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45104</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>45532.36847222222</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45565</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>44916.39701388889</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44453</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>44426</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>44490.66787037037</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>44438.86667824074</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>44858.42625</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>44781</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>44838.49244212963</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44404</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44732</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44781</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>44508.59416666667</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>44515.61378472222</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44504.28572916667</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>44496.35259259259</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44889.49348379629</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>44579</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44601.54201388889</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44418.4027199074</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>44544.60025462963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>44441.64387731482</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44431.39714120371</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44510.59653935185</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44468.40091435185</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>44517</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44510.59922453704</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>44503</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>44459</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>44390.47409722222</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>44390.49347222222</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>44592</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44819.35295138889</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44750</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44825</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>44418.68799768519</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44469</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>44424</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44460</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>44488.42238425926</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>44602</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>44379.73503472222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>44638</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44721</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44510</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44785.33260416667</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>44592.42363425926</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>44587</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>44385.55563657408</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>44782</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>44815.8621875</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44432</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>44435</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44375.609375</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44453.44710648148</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44504</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44580</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44691.34113425926</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44880</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44431.41829861111</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>44460.47375</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>44369</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44764.63974537037</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>44435</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44453.48915509259</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44434.61055555556</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44545.61800925926</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>44462</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44624</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44750.81856481481</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44446</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44515</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44477.3272337963</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44595.53233796296</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44392</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44375.66003472222</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44384</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44608</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44820.5830787037</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44816</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>44454.38134259259</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>44460</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>44461.37037037037</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44645</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44819.35944444445</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44656.46634259259</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44784.54667824074</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44721</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44585</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44585</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44585</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>44612</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>44834.35900462963</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44740</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>44750</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44440</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44587</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44470.34335648148</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>44424</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>44743</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>44564</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44474</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>44396.6427662037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>44392</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>44600.34350694445</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>44859</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>44593.88670138889</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>44362.50704861111</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>44743</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>44752</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>44778.37704861111</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>44504.29353009259</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>44477.338125</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>44482</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>44509.63892361111</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>44592.71334490741</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>44517</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44721.33517361111</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>44572.64497685185</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44841.35984953704</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>44888.42260416667</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>44368.54241898148</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>44364.465</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>44375.6222337963</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44587.36517361111</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>44655.39390046296</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44461</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44454</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>44834.76903935185</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>44459</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>44502.32267361111</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44515</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>44592</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44462</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44564.49002314815</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44398.715</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44781</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44531</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44365</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>44592</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44636.34431712963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44834</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44733</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>44683</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44463</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>44602</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44792.50780092592</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44827</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44657</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44902.45950231481</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44488</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45596.51546296296</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>44477.29997685185</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45351.72865740741</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45602</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45575.48229166667</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45561</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45251.44596064815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>44967.50171296296</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>44967.50269675926</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45775.46554398148</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>44792.50753472222</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>44592.50039351852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45597.60236111111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45265</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45267.5896412037</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44880.50373842593</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45569</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>45674.46950231482</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44903</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45580.55204861111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>44998.67371527778</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45278</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44936</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45175.33553240741</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45264.64685185185</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>44502.63461805556</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45702</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45663.61690972222</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45205</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45771.48474537037</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45771.48600694445</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>45672.34994212963</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45057</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>45930</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45188</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45259.69310185185</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45936.46378472223</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45936.56549768519</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44392.6381712963</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44582.62581018519</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>44431.4768287037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>44831.47726851852</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>45091.56835648148</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45134</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45341.54001157408</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45348.6049537037</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>44371</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45839.58662037037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45439.57853009259</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45201.67354166666</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45307.38616898148</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45944.46826388889</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45071.42814814814</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>44781</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45930</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45835.57190972222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45884.31612268519</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45783.7384375</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>44530</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45350.51460648148</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45946.48068287037</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45783.48454861111</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45135.48232638889</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>44851</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45950.44650462963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>44462.69760416666</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45953.67155092592</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45229.46152777778</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45055</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>44600</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45884.50511574074</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45888.35678240741</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45888.36869212963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45541.54959490741</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45677.5952662037</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45889</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45786.36444444444</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44710.46695601852</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45888</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45742.3846412037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45889.37385416667</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45888</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45888.35375</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45888</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45826.57552083334</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>45889.63392361111</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45742.38137731481</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45953.61858796296</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45406.36346064815</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45770.51099537037</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>44762.36475694444</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>44439</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44747.59320601852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45031.40950231482</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>44986.47112268519</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>45586.56929398148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>45839.50319444444</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>45623.62873842593</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45097.31440972222</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45097.42025462963</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>45335</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45965.63142361111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45384</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45434.5815625</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45439.3877662037</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45761.49452546296</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45645.50914351852</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45898.64612268518</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45104.51045138889</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45709.52268518518</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45645.54453703704</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45819.5825462963</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45737.51153935185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45587.46966435185</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45300</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45902.4108449074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45099</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45439.58064814815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45470.49353009259</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45309</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45309.59212962963</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45643.38037037037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45097.40740740741</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45272</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>44592</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45363</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45908</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45786.56335648148</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>45601.59809027778</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45456.52788194444</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>45716.6490162037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45645.71140046296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45623.50226851852</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45908</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45113.56304398148</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45911.62592592592</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>44949.40520833333</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>45911.62172453704</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>45309.60319444445</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44487</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45974.56275462963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>45161.49346064815</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45118.47174768519</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45975</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45336.70538194444</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45162</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45981.36712962963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45981.44628472222</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45414</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>45981.60770833334</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45226</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>45188.6525</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>44916.40381944444</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>44916.40960648148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>45982.43447916667</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45981.90465277778</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45701.6352662037</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>45082</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45461.56825231481</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45163.6054050926</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45188.73418981482</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>44655</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>45580.5847337963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45922.44916666667</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45191</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44952.40027777778</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>45209.4254050926</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45925.36075231482</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45925.36193287037</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44888.59611111111</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45925.35635416667</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45754.62920138889</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45754.63079861111</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45351.86930555556</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45628.61552083334</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45925.35803240741</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>44972.54766203704</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45992.571875</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45097.41377314815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45992.59366898148</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45992.57753472222</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>45992.5750462963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45992.59141203704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>44770</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45572.65032407407</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45999.74611111111</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45999.6591550926</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>44916.44489583333</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45190</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45930.49594907407</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45930</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>46001.634375</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45931.61743055555</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45930</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>44592.48420138889</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>45448.36395833334</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>45166.36192129629</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>46003</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45580.5531712963</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>46009.59636574074</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>46007.83314814815</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>46007.83997685185</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>46009.3007175926</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>45999.66931712963</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>46009.65798611111</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>46009.66805555556</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45625</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>45792.62685185186</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>44468</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>45362.56993055555</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>46010.3465625</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44781</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>45021</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>46010.32392361111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44977</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45545.90186342593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>45104.73398148148</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45645</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45645.81003472222</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45754.62659722222</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45827</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45135</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45135</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45135</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>44641</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44482.45895833334</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45042</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45329</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>45586.90974537037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45329</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45117</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>44888.59313657408</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>45099.47626157408</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>45610.86952546296</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>45742.45594907407</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>46003</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>46029.67594907407</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>44984.61899305556</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>46031.48685185185</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28656,7 +28656,7 @@
         <v>45228.48451388889</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>44748.65145833333</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>46031.41601851852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>46030.39181712963</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>46030.47910879629</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45441.46810185185</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45274.51340277777</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45736.59446759259</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>45741.51402777778</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45741.51513888889</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45728.66796296297</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         <v>46031</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45259</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>44693.3846875</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>45610</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45743</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>45595.47640046296</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45737.45528935185</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>45737</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45330.43899305556</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>45202.60905092592</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45702.43134259259</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45742</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45376.89543981481</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>45363</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>44916.40109953703</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>44531.43190972223</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>45733.54788194445</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>45733.55436342592</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>45803.47989583333</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45743</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45442</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>45708.456875</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45616.46105324074</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45359.58304398148</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45365</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45414.31138888889</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45107</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45251.44450231481</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>45805.30957175926</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45319.901875</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44515</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44984.61239583333</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>45232</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45462.58177083333</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44984.40798611111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44984.43561342593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>45357.63869212963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45048</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44824</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>46045.74806712963</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45672.34840277778</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45434.37204861111</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45581.72986111111</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>45811.6200925926</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44945</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>46044.49039351852</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>46045.7400462963</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45006.61266203703</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>46048.40107638889</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45615.56674768519</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45505</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>45069</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>46048.88774305556</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>46048.4884837963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45484.32416666667</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>46048.48978009259</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>46049.38795138889</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>46048.8853125</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>45015.67048611111</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45310</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45351.87196759259</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>45170.33331018518</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44728.60741898148</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45097</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45684.62931712963</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45330</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>44946</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>46055.49371527778</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>45170</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45107.55028935185</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45812.59789351852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45099</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45816.70986111111</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45133</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>45819.58771990741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44460.39493055556</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>45352</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>45792.55229166667</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45819.62290509259</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>45819.63070601852</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>45819.50528935185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45817.79064814815</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44837.49905092592</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45820.39466435185</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45351.71743055555</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>44434.58464120371</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>46062.3044212963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>46063.7453587963</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>46062.61298611111</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>46063.71168981482</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>46063.71476851852</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>46063.70391203704</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>44434</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>44484.32797453704</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>45673.74596064815</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>46064.43875</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>45748</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45748</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>44965.62542824074</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>46069.68664351852</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>44970</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45133</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45357.44114583333</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>46071</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45231.57694444444</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>44545.62172453704</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45681.37099537037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45152</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>44503</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>46077.64454861111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45230.33274305556</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>46077.60984953704</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44480.61528935185</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44741.47328703704</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>45272</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45084.49469907407</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44600.5731712963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>45331.45001157407</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>45331.47140046296</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45222</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44970</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45671.56422453704</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45435</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45230.33119212963</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45204.48375</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45455</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45835.36065972222</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45561</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>46084.5428587963</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>46084.55666666666</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>45282</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45737.45231481481</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45245.29518518518</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>45839.47649305555</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>46084.54674768518</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45838.35412037037</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>45839.5653587963</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>45631.34063657407</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45247</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>45838.42418981482</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45839.49872685185</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45838.43332175926</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45840.67126157408</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>45259.42446759259</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45840.6791087963</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45845.51800925926</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45548</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45729.334375</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>45748</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45747.57667824074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>46087.50570601852</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45625</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45715.48833333333</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>45715.48729166666</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>44834.77262731481</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>45370</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38255,7 +38255,7 @@
         <v>45847.59070601852</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>45322.49210648148</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>46091</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>45035</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>46092.32650462963</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>45645.80195601852</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45645.82511574074</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>46092.328125</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>45076</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38778,7 +38778,7 @@
         <v>45006.63824074074</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>44580.57619212963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>45089.59394675926</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45608.54987268519</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>44459</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45615.46576388889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45538.37537037037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>46002</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45298</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>46097.52116898148</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45372.87263888889</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45076.44001157407</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>46098.45064814815</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>44473.51526620371</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45170.51591435185</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45401.32675925926</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>44607</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
         <v>46099.49728009259</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39804,7 +39804,7 @@
         <v>44837.50092592592</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>45763.47391203704</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>46100.35878472222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>44511.41467592592</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>46104.32333333333</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>45089.45631944444</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>45443.44555555555</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>45240</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>46104.4325462963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>45168.39784722222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>46104.32527777777</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>46104.30789351852</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>45321.61387731481</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44363</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44470.34038194444</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>45163.63111111111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>46104.31443287037</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44510</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45852.58248842593</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45211.45560185185</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45414.37135416667</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45519.49717592593</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45314.72010416666</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45433.62693287037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45097.393125</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45448.36170138889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45645.81938657408</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>45645.82078703704</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45644.38033564815</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>46107.35502314815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>45649.29796296296</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45672.34774305556</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45163.67015046296</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>44549</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45322</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45582.63793981481</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45114</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>46107.3537037037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45860</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45005</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>44858.42417824074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45545.44009259259</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44564.48394675926</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45250.815</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>45224.41164351852</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>46107.3562037037</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>45814</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>46153.69381944444</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>46111.45739583333</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>45645.81774305556</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>45763.38681712963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>46111</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45672.35665509259</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45264.37290509259</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45525.62247685185</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43021,7 +43021,7 @@
         <v>44965.63684027778</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43078,7 +43078,7 @@
         <v>44926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>44926</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>45401.33418981481</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>45392.63688657407</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>46153.6920949074</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>46153.38778935185</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>45866.4878587963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
         <v>45288</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43534,7 +43534,7 @@
         <v>46153.36024305555</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>46153.36511574074</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>45733.55030092593</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45866.37274305556</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45866.48642361111</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>45394</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45113</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>46160.65711805555</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>44602</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>46160.75423611111</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>45007</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>44434.87822916666</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44434</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>46160.65570601852</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>46160.65982638889</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45568</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45297.71375</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45236.65589120371</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>45625</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>46161.44657407407</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45105</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>44859.57034722222</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>46161.81109953704</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45674.5233912037</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>46154.38048611111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44974,7 +44974,7 @@
         <v>44481</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45031,7 +45031,7 @@
         <v>46121.29490740741</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45874.57201388889</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>45875.56215277778</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>45873.84888888889</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>46122</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>45875.56143518518</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>45875.56277777778</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>44655</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>44970</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>45329</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>46121.29141203704</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>44847.45596064815</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45715,7 +45715,7 @@
         <v>45180.88775462963</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>45173</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45829,7 +45829,7 @@
         <v>45173</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>46126</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>45345.48063657407</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>45526.67918981481</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>45170.31317129629</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45170.3212037037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46163</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>44462</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45303</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>45303.40385416667</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>45882</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>46168.58686342592</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45104.41076388889</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45882</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46627,7 +46627,7 @@
         <v>46126</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>45113.57634259259</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>45988</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>45446.56364583333</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45438</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46912,7 +46912,7 @@
         <v>46128.36657407408</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>46128.37269675926</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>46128.37445601852</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>46128.37111111111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45884.51107638889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45182.44875</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45182.48945601852</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>46127</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>44607</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>44434.58464120371</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>46128.36802083333</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45669.82575231481</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>45315</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45462.56997685185</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>45449.4112962963</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>44463.63087962963</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47829,7 +47829,7 @@
         <v>45327</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>45164</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45330</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>46133</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48057,7 +48057,7 @@
         <v>46133</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>44995</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48171,7 +48171,7 @@
         <v>44442.57108796296</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48228,7 +48228,7 @@
         <v>45692.42841435185</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48285,7 +48285,7 @@
         <v>46175.48251157408</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45106.58976851852</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45574.51628472222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45616.67851851852</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>45639.45501157407</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>45510</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45219.46091435185</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45274</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45250.81989583333</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>44587.3328587963</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>44783.50346064815</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>44830</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45544.37059027778</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>45133</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45408.44111111111</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>44834.65052083333</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45366.75533564815</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>44815.87179398148</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45069.68887731482</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>45440</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>46177.56504629629</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>45701.63836805556</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45302.6671875</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45615.56019675926</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45113.57435185185</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>45903.39982638889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>44683</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45546.33434027778</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>44839.57224537037</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>44970</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>45222</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50067,7 +50067,7 @@
         <v>45183.31346064815</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45839.28930555555</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>44965</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45699.5131712963</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45827</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45000</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>46037.64554398148</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45944.69631944445</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45112.395625</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45183.47331018518</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>46178.28261574074</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45775</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45706.42435185185</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45891</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45313</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45799</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45306.66175925926</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>44839</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>44753</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45135</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>46178.29589120371</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45931.70164351852</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>44510.60637731481</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>46178.29810185185</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45895</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>44802</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45446.46471064815</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>45883.40858796296</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51668,7 +51668,7 @@
         <v>44929.3943287037</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>44743</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>44481.3784375</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>46178.29991898148</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>45170.35475694444</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51953,7 +51953,7 @@
         <v>45497.3596875</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52010,7 +52010,7 @@
         <v>45497.36287037037</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52067,7 +52067,7 @@
         <v>46178.36899305556</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>44462.69760416666</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52181,7 +52181,7 @@
         <v>45902.38627314815</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>45119</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45119.67211805555</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45401.54920138889</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>46112.39207175926</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52471,7 +52471,7 @@
         <v>45965.45693287037</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>44952</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45112.59065972222</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>45400</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45525.63314814815</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52761,7 +52761,7 @@
         <v>45107.37986111111</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>44747.48467592592</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45785.71899305555</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52932,7 +52932,7 @@
         <v>45526.68496527777</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52989,7 +52989,7 @@
         <v>44600</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53046,7 +53046,7 @@
         <v>45912.6409375</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45840.65412037037</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>45569.31168981481</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53217,7 +53217,7 @@
         <v>45866.33217592593</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53274,7 +53274,7 @@
         <v>44930</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53331,7 +53331,7 @@
         <v>45925.3837037037</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>45971</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53445,7 +53445,7 @@
         <v>45033</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>45572</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53559,7 +53559,7 @@
         <v>45742</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53616,7 +53616,7 @@
         <v>45341.64803240741</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53673,7 +53673,7 @@
         <v>46006.71462962963</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53730,7 +53730,7 @@
         <v>45763.38805555556</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53787,7 +53787,7 @@
         <v>45348.60625</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53844,7 +53844,7 @@
         <v>45693.37408564815</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53901,7 +53901,7 @@
         <v>45889.6171875</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53958,7 +53958,7 @@
         <v>45785.66460648148</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54015,7 +54015,7 @@
         <v>44740</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54077,7 +54077,7 @@
         <v>45406.31430555556</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54134,7 +54134,7 @@
         <v>44998.57355324074</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54191,7 +54191,7 @@
         <v>46178.29085648148</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>46178.2947337963</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>46178</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45302</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>44869</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>45841.679375</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>46178.28458333333</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>46136.62380787037</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45174.64620370371</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45608.54881944445</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54761,7 +54761,7 @@
         <v>45873.59123842593</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54818,7 +54818,7 @@
         <v>46178.28552083333</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54875,7 +54875,7 @@
         <v>45971</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54932,7 +54932,7 @@
         <v>45610.38314814815</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54989,7 +54989,7 @@
         <v>46122.9083912037</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55046,7 +55046,7 @@
         <v>45153.53380787037</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
         <v>45755.66511574074</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55160,7 +55160,7 @@
         <v>45670.57231481482</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>45825.60899305555</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55274,7 +55274,7 @@
         <v>45348</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45839.31964120371</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55388,7 +55388,7 @@
         <v>45363</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45363</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>45363</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55574,7 +55574,7 @@
         <v>45364.29489583334</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55631,7 +55631,7 @@
         <v>45880</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55688,7 +55688,7 @@
         <v>45104</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55745,7 +55745,7 @@
         <v>44538.319375</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55802,7 +55802,7 @@
         <v>45281.52006944444</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55859,7 +55859,7 @@
         <v>45525.60603009259</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>44785.3465162037</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55973,7 +55973,7 @@
         <v>46052.47891203704</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56030,7 +56030,7 @@
         <v>45883.40668981482</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56087,7 +56087,7 @@
         <v>45006.65795138889</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56144,7 +56144,7 @@
         <v>45202</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56201,7 +56201,7 @@
         <v>45563</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56263,7 +56263,7 @@
         <v>44447.46810185185</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56320,7 +56320,7 @@
         <v>45357.54391203704</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         <v>45691.5809837963</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56439,7 +56439,7 @@
         <v>45173</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56496,7 +56496,7 @@
         <v>45629.60505787037</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56553,7 +56553,7 @@
         <v>45314.61902777778</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56610,7 +56610,7 @@
         <v>44448.65282407407</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56672,7 +56672,7 @@
         <v>45420.6628125</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56729,7 +56729,7 @@
         <v>45195.6445949074</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56786,7 +56786,7 @@
         <v>46182.55842592593</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56843,7 +56843,7 @@
         <v>45238.34974537037</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>44880.49763888889</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>44880.50003472222</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45079</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>45091</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45378</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45616.64181712963</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57247,7 +57247,7 @@
         <v>45827</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>44602</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45163</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57418,7 +57418,7 @@
         <v>46182.5702662037</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>44523.60070601852</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>44677.47850694445</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45303</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>44592.47372685185</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57703,7 +57703,7 @@
         <v>46182.56318287037</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45475.33333333334</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45211.4853125</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45589.45113425926</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45352</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45538</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45329</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58107,7 +58107,7 @@
         <v>45314</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58164,7 +58164,7 @@
         <v>45645.81355324074</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>44815.86887731482</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>44497.59402777778</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58340,7 +58340,7 @@
         <v>45754.61956018519</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58402,7 +58402,7 @@
         <v>45091.57478009259</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58459,7 +58459,7 @@
         <v>45022</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58516,7 +58516,7 @@
         <v>45526.66983796296</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58573,7 +58573,7 @@
         <v>45114</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>46185.62405092592</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58687,7 +58687,7 @@
         <v>46185.45840277777</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45440.66215277778</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58801,7 +58801,7 @@
         <v>44587.32568287037</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>44715.42476851852</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58915,7 +58915,7 @@
         <v>44813</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>45365.64836805555</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59029,7 +59029,7 @@
         <v>45385</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>44946</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59143,7 +59143,7 @@
         <v>44805.27554398148</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59200,7 +59200,7 @@
         <v>44813</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59257,7 +59257,7 @@
         <v>45398.62652777778</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59314,7 +59314,7 @@
         <v>45307.34739583333</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59371,7 +59371,7 @@
         <v>44825</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59428,7 +59428,7 @@
         <v>44917</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59485,7 +59485,7 @@
         <v>45177</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59547,7 +59547,7 @@
         <v>45174.35186342592</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>45329</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59666,7 +59666,7 @@
         <v>45245.48828703703</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>44398</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59780,7 +59780,7 @@
         <v>45737</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>45719.45905092593</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59894,7 +59894,7 @@
         <v>45364.88361111111</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>45089.60100694445</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60008,7 +60008,7 @@
         <v>44459.33054398148</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60065,7 +60065,7 @@
         <v>45660</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60122,7 +60122,7 @@
         <v>45107</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60179,7 +60179,7 @@
         <v>45184.57670138889</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60236,7 +60236,7 @@
         <v>45589.5802662037</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60293,7 +60293,7 @@
         <v>45589.61851851852</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60350,7 +60350,7 @@
         <v>45532.6524537037</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60407,7 +60407,7 @@
         <v>44392.49893518518</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60464,7 +60464,7 @@
         <v>44392.6381712963</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60521,7 +60521,7 @@
         <v>45370</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60578,7 +60578,7 @@
         <v>45406.34086805556</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60635,7 +60635,7 @@
         <v>44595.52881944444</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60692,7 +60692,7 @@
         <v>45104.73836805556</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60749,7 +60749,7 @@
         <v>45071</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60806,7 +60806,7 @@
         <v>44816</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60863,7 +60863,7 @@
         <v>45216.33821759259</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60920,7 +60920,7 @@
         <v>45303.34582175926</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>45678.47584490741</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>45182.62420138889</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61091,7 +61091,7 @@
         <v>44495</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61148,7 +61148,7 @@
         <v>44833</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61205,7 +61205,7 @@
         <v>45219</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61262,7 +61262,7 @@
         <v>45030.45988425926</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61319,7 +61319,7 @@
         <v>45544.34594907407</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61376,7 +61376,7 @@
         <v>45211</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61433,7 +61433,7 @@
         <v>45691.61326388889</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61490,7 +61490,7 @@
         <v>44488.41871527778</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61547,7 +61547,7 @@
         <v>45631.55684027778</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61604,7 +61604,7 @@
         <v>45216.36305555556</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61666,7 +61666,7 @@
         <v>45359.59966435185</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61723,7 +61723,7 @@
         <v>45376.32592592593</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61780,7 +61780,7 @@
         <v>44810.47083333333</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61837,7 +61837,7 @@
         <v>45209</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61894,7 +61894,7 @@
         <v>45183.33701388889</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61951,7 +61951,7 @@
         <v>45595.68493055556</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>45575.49151620371</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62065,7 +62065,7 @@
         <v>45062</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62122,7 +62122,7 @@
         <v>45231.61479166667</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62179,7 +62179,7 @@
         <v>45699.97146990741</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>45737</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62293,7 +62293,7 @@
         <v>44930</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62350,7 +62350,7 @@
         <v>44971</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62407,7 +62407,7 @@
         <v>45602.43070601852</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45092.40048611111</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45674.52591435185</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>45478</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>45769.80791666666</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62697,7 +62697,7 @@
         <v>45164.86072916666</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62754,7 +62754,7 @@
         <v>45309</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>45309</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62868,7 +62868,7 @@
         <v>45182.45072916667</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62930,7 +62930,7 @@
         <v>45329</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>45222</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>45337</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63101,7 +63101,7 @@
         <v>45492.52554398148</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45323.41452546296</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>45763.59106481481</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63272,7 +63272,7 @@
         <v>45384.44951388889</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>45296</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63386,7 +63386,7 @@
         <v>45763.37726851852</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63443,7 +63443,7 @@
         <v>45763.37920138889</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63500,7 +63500,7 @@
         <v>45763.38908564814</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63557,7 +63557,7 @@
         <v>44946</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63614,7 +63614,7 @@
         <v>45462</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>44407.60175925926</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63728,7 +63728,7 @@
         <v>44879</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63785,7 +63785,7 @@
         <v>45719.65729166667</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63842,7 +63842,7 @@
         <v>45540.36818287037</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63899,7 +63899,7 @@
         <v>45134.50414351852</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63956,7 +63956,7 @@
         <v>45310</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64013,7 +64013,7 @@
         <v>45316.50005787037</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64070,7 +64070,7 @@
         <v>45414.36013888889</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64127,7 +64127,7 @@
         <v>45607</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64184,7 +64184,7 @@
         <v>44818.64456018519</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64241,7 +64241,7 @@
         <v>45673.45511574074</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64298,7 +64298,7 @@
         <v>44831</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64355,7 +64355,7 @@
         <v>45001</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64417,7 +64417,7 @@
         <v>45254.60143518518</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64479,7 +64479,7 @@
         <v>45090.59459490741</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64536,7 +64536,7 @@
         <v>45132.64173611111</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64593,7 +64593,7 @@
         <v>45335</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -64650,7 +64650,7 @@
         <v>45602.43329861111</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -64707,7 +64707,7 @@
         <v>44963.8266087963</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -64764,7 +64764,7 @@
         <v>45168.70575231482</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -64821,7 +64821,7 @@
         <v>45400.6177662037</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -64878,7 +64878,7 @@
         <v>45188.66708333333</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -64935,7 +64935,7 @@
         <v>45670.57783564815</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -64992,7 +64992,7 @@
         <v>44902.52461805556</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>44564</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65111,7 +65111,7 @@
         <v>45189.39834490741</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -65173,7 +65173,7 @@
         <v>45691.65603009259</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -65230,7 +65230,7 @@
         <v>44916.41415509259</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -65287,7 +65287,7 @@
         <v>44957.61083333333</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>44817</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44890</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>45957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45520</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45754</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>44612</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44840</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>44908</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>46002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>46100</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>45819</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>46188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>46163</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>45583</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44819</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45763</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45477</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>46045</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45814</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>45048</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45599</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44468</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45713</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45673</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>45891</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>44572</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45303</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45148</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>46166</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45357</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45616</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45035</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45400</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45211</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45310</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45792</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>45835</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45840</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45860</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45106</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>45497</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>45201</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45539</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>46051</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44462</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44721</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>44454</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44592</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44740</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>45596</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44830</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>45597</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>45555</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44781</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>45021</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44748</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44824</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45240</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>44728</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45342</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45835</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45775</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45586</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>45672</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>45904</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44434</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>45645</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45239</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45880</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>46141</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>44998</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44880</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>46188</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45419</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45085</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45408</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>45930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45119</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>45009</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>46069</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>46071</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>45261</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>45378</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45104</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>44816</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45532</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>44833</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>45337</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44916</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>45352</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45643</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>45791</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>45736</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>45820</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45839</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>45713</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45604</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>45497</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>45614</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>45742</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44453</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>44490</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>44438</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>44426</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44858</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>44838</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>44781</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>44404</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>44732</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>44515</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44508</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44504</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44496</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>44579</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>44889</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44601</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>44418</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>44544</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>44441</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>44510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>44468</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44431</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>44517</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>44764</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>44510</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>44503</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44459</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44592</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>44819</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>44750</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>44825</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>44418</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44424</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>44460</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>44488</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>44638</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>44510</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>44721</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>44785</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>44592</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44602</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44587</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>44782</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>44815</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44432</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>44435</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44453</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44504</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44580</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44880</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>44691</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44431</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>44460</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>44434</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44435</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>44453</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44462</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>44545</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44750</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44624</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44446</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>44477</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>44595</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>44608</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44454</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>44820</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>44460</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>44816</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>44461</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>44819</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>44645</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>44656</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>44784</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44585</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>44585</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>44585</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44834</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44740</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>44750</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>44440</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44587</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>44743</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>44474</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>44600</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>44859</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>44593</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>44743</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44778</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44504</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>44834</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44424</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>44477</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44482</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>44509</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>44592</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44517</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44572</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44721</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>44841</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44888</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>44587</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>44655</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44461</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>44454</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>44459</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>44502</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>44515</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44592</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>44462</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>44564</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>44781</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>44531</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44636</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44834</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>44733</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>44683</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>44463</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>44602</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44657</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>44827</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>44792</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>44902</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44488</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>44477</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>45351</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>45602</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>44967</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>44967</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45575</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45775</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>44792</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>44592</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45674</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>45580</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44998</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>45561</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44903</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>45663</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44936</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45205</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>45771</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45771</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45175</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45251</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45264</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45057</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45278</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>45259</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>44582</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45091</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>44831</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45188</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45307</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>44530</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45350</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44851</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>45071</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45265</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>45135</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45229</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45055</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45267</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>44600</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45406</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>44439</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44880</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44762</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>45569</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>44710</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>44747</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>45384</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>45031</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>45434</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45104</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>44986</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45439</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45709</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>45645</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45645</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45300</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>45099</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45309</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>45470</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45309</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45097</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45272</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>45363</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45118</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>44949</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45309</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>44487</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45113</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>45161</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45336</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>44916</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44916</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45701</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>45097</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28604,7 +28604,7 @@
         <v>45097</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>45162</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>45580</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45082</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45461</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>45414</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45163</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45188</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>44655</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45191</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45226</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45188</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44952</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45754</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45754</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>45351</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>45628</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>45209</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29933,7 +29933,7 @@
         <v>44972</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>44888</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>45335</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>44916</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45097</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>44770</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45572</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45190</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>44592</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>45448</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45362</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>45166</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45580</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>45104</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45625</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45645</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45645</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>45754</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45117</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>44641</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>44482</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>44977</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45135</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>45135</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45135</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>45042</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44888</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45329</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45586</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45329</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45099</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>44984</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45610</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45742</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45441</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45228</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>44693</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45274</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>45330</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>45363</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>44916</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45202</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45702</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45545</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>45595</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44531</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45376</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45251</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45365</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45414</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45048</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45319</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44515</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>44984</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45107</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>45006</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45232</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45581</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>45069</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>44945</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>45015</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>45310</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45351</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>45484</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>45170</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45462</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45097</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>45684</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>45330</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>44946</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>45201</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>45107</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>44984</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>44984</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45357</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>45874</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45875</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45099</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>45875</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>45875</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45884</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>44460</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45352</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>45839</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44837</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>45882</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45882</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45351</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45699</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45827</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>44434</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>46037</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45944</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45112</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44462</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45884</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45891</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>44434</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45313</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45799</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>45306</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>45888</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45888</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45541</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37560,7 +37560,7 @@
         <v>45677</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45889</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>45786</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>45888</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>45742</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>44434</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45889</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45888</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38144,7 +38144,7 @@
         <v>45888</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45888</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44484</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38363,7 +38363,7 @@
         <v>45826</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38436,7 +38436,7 @@
         <v>45889</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45742</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38582,7 +38582,7 @@
         <v>45770</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>45748</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>45748</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45931</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>44510</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>45895</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45839</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>44965</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>45623</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>45883</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>45341</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39395,7 +39395,7 @@
         <v>44970</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>45839</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45133</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>45357</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>45898</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39760,7 +39760,7 @@
         <v>45902</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>46112</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45231</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>45819</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>45965</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40130,7 +40130,7 @@
         <v>45737</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>45587</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>45525</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40349,7 +40349,7 @@
         <v>45902</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>45785</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44545</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>45681</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>45152</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>44503</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>45912</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>45230</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>45840</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>45866</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>44480</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>44741</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45925</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45272</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45084</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>45971</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>44600</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>45911</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>45331</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>45331</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45911</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45222</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>46006</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>45763</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>44970</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>45671</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45435</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45230</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45204</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45693</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>45889</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45455</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45785</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42768,7 +42768,7 @@
         <v>45561</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42841,7 +42841,7 @@
         <v>45282</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>45245</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>45841</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>45631</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45247</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>45259</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>46136</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>45608</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45873</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45922</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45370</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45322</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45971</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>45610</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>46122</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43936,7 +43936,7 @@
         <v>45153</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>45755</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45925</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45670</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45925</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45035</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45825</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45348</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         <v>45839</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45645</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45645</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>45925</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45076</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45006</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>44538</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>44785</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>44580</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>46052</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45260,7 +45260,7 @@
         <v>45883</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>45089</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>45691</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>44459</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>45615</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45538</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45298</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45930</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>45931</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45930</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>45372</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45076</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>44473</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>45170</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45401</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>44607</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46443,7 +46443,7 @@
         <v>45936</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44837</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46589,7 +46589,7 @@
         <v>45936</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
         <v>44511</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>45089</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45443</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45240</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45168</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47027,7 +47027,7 @@
         <v>45827</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47100,7 +47100,7 @@
         <v>45321</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47173,7 +47173,7 @@
         <v>44470</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47246,7 +47246,7 @@
         <v>45163</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44510</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45944</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45589</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>45211</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45946</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47684,7 +47684,7 @@
         <v>45414</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>44894</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>45519</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45314</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47976,7 +47976,7 @@
         <v>45433</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45097</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>45448</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>45950</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>45645</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>45645</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45953</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48497,7 +48497,7 @@
         <v>45644</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48570,7 +48570,7 @@
         <v>45953</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>45649</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>46188</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45114</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48867,7 +48867,7 @@
         <v>44858</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45545</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>45250</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49086,7 +49086,7 @@
         <v>45224</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>45645</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>45763</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45672</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         <v>45965</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49461,7 +49461,7 @@
         <v>45264</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45525</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>44965</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>44926</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>44926</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45401</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45392</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45394</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>46190</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>44602</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50191,7 +50191,7 @@
         <v>45007</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>44434</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>44434</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50415,7 +50415,7 @@
         <v>45974</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45568</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50566,7 +50566,7 @@
         <v>45975</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45297</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>46153</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50785,7 +50785,7 @@
         <v>45236</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50858,7 +50858,7 @@
         <v>45625</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45105</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51004,7 +51004,7 @@
         <v>44859</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51077,7 +51077,7 @@
         <v>46195</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45981</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51228,7 +51228,7 @@
         <v>45981</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51301,7 +51301,7 @@
         <v>45674</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45981</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51447,7 +51447,7 @@
         <v>45982</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51520,7 +51520,7 @@
         <v>45981</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>46153</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>44481</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>46153</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>44655</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51885,7 +51885,7 @@
         <v>46153</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>44970</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52031,7 +52031,7 @@
         <v>45329</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>44847</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52177,7 +52177,7 @@
         <v>45180</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52250,7 +52250,7 @@
         <v>45173</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45173</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52396,7 +52396,7 @@
         <v>45992</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52469,7 +52469,7 @@
         <v>45992</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>46153</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52615,7 +52615,7 @@
         <v>45992</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52688,7 +52688,7 @@
         <v>45992</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52761,7 +52761,7 @@
         <v>45992</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45345</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45526</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52980,7 +52980,7 @@
         <v>45170</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53053,7 +53053,7 @@
         <v>45170</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>45303</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53199,7 +53199,7 @@
         <v>45999</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45999</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53345,7 +53345,7 @@
         <v>45104</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53418,7 +53418,7 @@
         <v>46154</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53496,7 +53496,7 @@
         <v>46197</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53569,7 +53569,7 @@
         <v>45113</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53642,7 +53642,7 @@
         <v>45866</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53715,7 +53715,7 @@
         <v>45446</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53788,7 +53788,7 @@
         <v>46001</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45438</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45639</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54007,7 +54007,7 @@
         <v>46197</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54080,7 +54080,7 @@
         <v>46003</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54153,7 +54153,7 @@
         <v>45182</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>45182</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>46196</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54377,7 +54377,7 @@
         <v>44607</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>46009</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54523,7 +54523,7 @@
         <v>46126</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>46007</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54669,7 +54669,7 @@
         <v>46007</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54742,7 +54742,7 @@
         <v>46009</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54815,7 +54815,7 @@
         <v>45669</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45999</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54961,7 +54961,7 @@
         <v>46009</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>46009</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45315</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55180,7 +55180,7 @@
         <v>45462</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55253,7 +55253,7 @@
         <v>45449</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55326,7 +55326,7 @@
         <v>46196</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55399,7 +55399,7 @@
         <v>46010</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>44463</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55545,7 +55545,7 @@
         <v>45327</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>45164</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45330</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>46010</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55837,7 +55837,7 @@
         <v>44995</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55910,7 +55910,7 @@
         <v>44442</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55983,7 +55983,7 @@
         <v>45692</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45827</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56129,7 +56129,7 @@
         <v>45106</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56202,7 +56202,7 @@
         <v>45574</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>45616</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56353,7 +56353,7 @@
         <v>45510</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>45219</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>45274</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45250</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56650,7 +56650,7 @@
         <v>45400</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>46003</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>44587</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>46029</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>44783</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>46160</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>46031</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57166,7 +57166,7 @@
         <v>44830</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>46031</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>45544</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
         <v>45133</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45408</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57531,7 +57531,7 @@
         <v>46161</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57604,7 +57604,7 @@
         <v>46030</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>44834</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57750,7 +57750,7 @@
         <v>46030</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57823,7 +57823,7 @@
         <v>45366</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57896,7 +57896,7 @@
         <v>44815</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57969,7 +57969,7 @@
         <v>46160</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58042,7 +58042,7 @@
         <v>46031</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45069</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58188,7 +58188,7 @@
         <v>45440</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45761</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>45701</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45302</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58485,7 +58485,7 @@
         <v>46202</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45615</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>45113</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58704,7 +58704,7 @@
         <v>46160</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58777,7 +58777,7 @@
         <v>46064</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>44683</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58923,7 +58923,7 @@
         <v>45930</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>45546</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>44839</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>44970</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>45222</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45183</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59361,7 +59361,7 @@
         <v>44965</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59434,7 +59434,7 @@
         <v>46160</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59507,7 +59507,7 @@
         <v>45000</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59580,7 +59580,7 @@
         <v>45183</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59653,7 +59653,7 @@
         <v>45706</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59726,7 +59726,7 @@
         <v>44839</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>44753</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59872,7 +59872,7 @@
         <v>46163</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59945,7 +59945,7 @@
         <v>45135</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60018,7 +60018,7 @@
         <v>46044</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>46045</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60164,7 +60164,7 @@
         <v>46048</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>46048</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>46048</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>46049</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60456,7 +60456,7 @@
         <v>46048</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>44802</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>45446</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>46161</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60753,7 +60753,7 @@
         <v>44929</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60826,7 +60826,7 @@
         <v>44743</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>44481</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>46204</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>45170</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61118,7 +61118,7 @@
         <v>45497</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61191,7 +61191,7 @@
         <v>45497</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>46055</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61337,7 +61337,7 @@
         <v>45133</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61410,7 +61410,7 @@
         <v>44462</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61483,7 +61483,7 @@
         <v>45119</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61556,7 +61556,7 @@
         <v>45401</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61629,7 +61629,7 @@
         <v>44952</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61702,7 +61702,7 @@
         <v>45112</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61775,7 +61775,7 @@
         <v>45107</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61848,7 +61848,7 @@
         <v>44747</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61921,7 +61921,7 @@
         <v>46062</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61994,7 +61994,7 @@
         <v>45526</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>46063</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62140,7 +62140,7 @@
         <v>44600</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62213,7 +62213,7 @@
         <v>46062</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62286,7 +62286,7 @@
         <v>46063</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>46063</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62432,7 +62432,7 @@
         <v>46063</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62505,7 +62505,7 @@
         <v>45930</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45569</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>44930</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45033</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>46069</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>45572</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62948,7 +62948,7 @@
         <v>45341</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45348</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63094,7 +63094,7 @@
         <v>46077</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63167,7 +63167,7 @@
         <v>46077</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63240,7 +63240,7 @@
         <v>44740</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63318,7 +63318,7 @@
         <v>45406</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63391,7 +63391,7 @@
         <v>44998</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>45302</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63537,7 +63537,7 @@
         <v>44869</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63610,7 +63610,7 @@
         <v>46168</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63683,7 +63683,7 @@
         <v>45174</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63756,7 +63756,7 @@
         <v>46084</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>46084</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63902,7 +63902,7 @@
         <v>46084</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63975,7 +63975,7 @@
         <v>45363</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>45363</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64131,7 +64131,7 @@
         <v>45363</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64209,7 +64209,7 @@
         <v>45364</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64282,7 +64282,7 @@
         <v>46213</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64355,7 +64355,7 @@
         <v>45104</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64428,7 +64428,7 @@
         <v>45281</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64501,7 +64501,7 @@
         <v>45525</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64574,7 +64574,7 @@
         <v>45006</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64647,7 +64647,7 @@
         <v>45202</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64720,7 +64720,7 @@
         <v>45563</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64798,7 +64798,7 @@
         <v>44447</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64871,7 +64871,7 @@
         <v>45357</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64944,7 +64944,7 @@
         <v>46087</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65017,7 +65017,7 @@
         <v>46091</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65090,7 +65090,7 @@
         <v>45173</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65163,7 +65163,7 @@
         <v>46092</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65236,7 +65236,7 @@
         <v>46092</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65309,7 +65309,7 @@
         <v>45629</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65382,7 +65382,7 @@
         <v>46002</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65455,7 +65455,7 @@
         <v>45314</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65528,7 +65528,7 @@
         <v>46097</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65601,7 +65601,7 @@
         <v>44448</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65679,7 +65679,7 @@
         <v>46098</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65752,7 +65752,7 @@
         <v>45420</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65825,7 +65825,7 @@
         <v>45195</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65898,7 +65898,7 @@
         <v>45238</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65976,7 +65976,7 @@
         <v>46099</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66049,7 +66049,7 @@
         <v>44880</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66122,7 +66122,7 @@
         <v>44880</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66195,7 +66195,7 @@
         <v>45079</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66268,7 +66268,7 @@
         <v>45091</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66341,7 +66341,7 @@
         <v>46100</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66414,7 +66414,7 @@
         <v>46104</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66487,7 +66487,7 @@
         <v>46104</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66560,7 +66560,7 @@
         <v>46104</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66633,7 +66633,7 @@
         <v>44602</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66706,7 +66706,7 @@
         <v>45163</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66779,7 +66779,7 @@
         <v>44523</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66852,7 +66852,7 @@
         <v>44677</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66925,7 +66925,7 @@
         <v>45303</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66998,7 +66998,7 @@
         <v>44592</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67071,7 +67071,7 @@
         <v>46107</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67144,7 +67144,7 @@
         <v>46107</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67217,7 +67217,7 @@
         <v>46175</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67290,7 +67290,7 @@
         <v>45475</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67363,7 +67363,7 @@
         <v>46107</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67436,7 +67436,7 @@
         <v>46111</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67509,7 +67509,7 @@
         <v>46111</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67582,7 +67582,7 @@
         <v>45211</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67655,7 +67655,7 @@
         <v>45352</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67728,7 +67728,7 @@
         <v>45538</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67801,7 +67801,7 @@
         <v>45329</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67879,7 +67879,7 @@
         <v>45314</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67952,7 +67952,7 @@
         <v>45645</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68030,7 +68030,7 @@
         <v>44815</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68103,7 +68103,7 @@
         <v>46178</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68176,7 +68176,7 @@
         <v>44497</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68249,7 +68249,7 @@
         <v>45091</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68322,7 +68322,7 @@
         <v>45022</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68395,7 +68395,7 @@
         <v>45526</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68468,7 +68468,7 @@
         <v>45114</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68541,7 +68541,7 @@
         <v>46121</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68614,7 +68614,7 @@
         <v>46122</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68687,7 +68687,7 @@
         <v>46178</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68760,7 +68760,7 @@
         <v>46121</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68833,7 +68833,7 @@
         <v>45440</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68906,7 +68906,7 @@
         <v>46178</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68979,7 +68979,7 @@
         <v>44587</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69052,7 +69052,7 @@
         <v>44462</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69125,7 +69125,7 @@
         <v>44715</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69198,7 +69198,7 @@
         <v>44813</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69271,7 +69271,7 @@
         <v>46178</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69344,7 +69344,7 @@
         <v>46178</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69417,7 +69417,7 @@
         <v>46178</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69490,7 +69490,7 @@
         <v>46178</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69563,7 +69563,7 @@
         <v>45365</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69636,7 +69636,7 @@
         <v>46178</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69709,7 +69709,7 @@
         <v>46178</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69782,7 +69782,7 @@
         <v>46126</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69855,7 +69855,7 @@
         <v>46128</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69928,7 +69928,7 @@
         <v>46128</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70001,7 +70001,7 @@
         <v>46128</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70074,7 +70074,7 @@
         <v>46128</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70147,7 +70147,7 @@
         <v>45385</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70220,7 +70220,7 @@
         <v>46177</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70293,7 +70293,7 @@
         <v>46127</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70366,7 +70366,7 @@
         <v>46182</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70439,7 +70439,7 @@
         <v>46182</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70512,7 +70512,7 @@
         <v>46128</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70585,7 +70585,7 @@
         <v>44946</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70658,7 +70658,7 @@
         <v>46133</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70731,7 +70731,7 @@
         <v>46133</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>46182</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70877,7 +70877,7 @@
         <v>44805</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70950,7 +70950,7 @@
         <v>44813</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71023,7 +71023,7 @@
         <v>45903</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71096,7 +71096,7 @@
         <v>45398</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71169,7 +71169,7 @@
         <v>46185</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71242,7 +71242,7 @@
         <v>46184</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71315,7 +71315,7 @@
         <v>45307</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71388,7 +71388,7 @@
         <v>44825</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71461,7 +71461,7 @@
         <v>44917</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71534,7 +71534,7 @@
         <v>45177</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71612,7 +71612,7 @@
         <v>45174</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71690,7 +71690,7 @@
         <v>45329</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71763,7 +71763,7 @@
         <v>46184</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71836,7 +71836,7 @@
         <v>45245</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71909,7 +71909,7 @@
         <v>45737</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71982,7 +71982,7 @@
         <v>45719</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72055,7 +72055,7 @@
         <v>45364</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72128,7 +72128,7 @@
         <v>46185</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72201,7 +72201,7 @@
         <v>46184</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72274,7 +72274,7 @@
         <v>45089</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72347,7 +72347,7 @@
         <v>44459</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72420,7 +72420,7 @@
         <v>45660</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72493,7 +72493,7 @@
         <v>45107</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72566,7 +72566,7 @@
         <v>45184</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72639,7 +72639,7 @@
         <v>45589</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72712,7 +72712,7 @@
         <v>45589</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72785,7 +72785,7 @@
         <v>45532</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72858,7 +72858,7 @@
         <v>45370</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72931,7 +72931,7 @@
         <v>45406</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73004,7 +73004,7 @@
         <v>44595</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73077,7 +73077,7 @@
         <v>45104</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73150,7 +73150,7 @@
         <v>45071</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73223,7 +73223,7 @@
         <v>45216</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73296,7 +73296,7 @@
         <v>45303</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73369,7 +73369,7 @@
         <v>45678</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73442,7 +73442,7 @@
         <v>45182</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73515,7 +73515,7 @@
         <v>44495</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73588,7 +73588,7 @@
         <v>45219</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73661,7 +73661,7 @@
         <v>45030</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73734,7 +73734,7 @@
         <v>45544</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73807,7 +73807,7 @@
         <v>45691</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73880,7 +73880,7 @@
         <v>44488</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73953,7 +73953,7 @@
         <v>45631</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74026,7 +74026,7 @@
         <v>45216</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74104,7 +74104,7 @@
         <v>45359</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74177,7 +74177,7 @@
         <v>45376</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74250,7 +74250,7 @@
         <v>44810</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74323,7 +74323,7 @@
         <v>45209</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74396,7 +74396,7 @@
         <v>45183</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74469,7 +74469,7 @@
         <v>45595</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74542,7 +74542,7 @@
         <v>45575</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74615,7 +74615,7 @@
         <v>45062</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74688,7 +74688,7 @@
         <v>45231</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74761,7 +74761,7 @@
         <v>45699</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74834,7 +74834,7 @@
         <v>45737</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74907,7 +74907,7 @@
         <v>44930</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74980,7 +74980,7 @@
         <v>44971</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75053,7 +75053,7 @@
         <v>45602</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75126,7 +75126,7 @@
         <v>45092</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75199,7 +75199,7 @@
         <v>45674</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75272,7 +75272,7 @@
         <v>45478</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75345,7 +75345,7 @@
         <v>45769</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75423,7 +75423,7 @@
         <v>45164</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75496,7 +75496,7 @@
         <v>45309</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75569,7 +75569,7 @@
         <v>45309</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75642,7 +75642,7 @@
         <v>45182</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75720,7 +75720,7 @@
         <v>45329</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75793,7 +75793,7 @@
         <v>45222</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75866,7 +75866,7 @@
         <v>45492</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75939,7 +75939,7 @@
         <v>45323</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76012,7 +76012,7 @@
         <v>45763</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76085,7 +76085,7 @@
         <v>45384</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76158,7 +76158,7 @@
         <v>45296</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76231,7 +76231,7 @@
         <v>45763</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76304,7 +76304,7 @@
         <v>45763</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76377,7 +76377,7 @@
         <v>45763</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76450,7 +76450,7 @@
         <v>44946</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76523,7 +76523,7 @@
         <v>45462</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76596,7 +76596,7 @@
         <v>44407</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76669,7 +76669,7 @@
         <v>44879</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76742,7 +76742,7 @@
         <v>45719</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76815,7 +76815,7 @@
         <v>45540</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76888,7 +76888,7 @@
         <v>45134</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76961,7 +76961,7 @@
         <v>45316</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77034,7 +77034,7 @@
         <v>45414</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77107,7 +77107,7 @@
         <v>45607</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77180,7 +77180,7 @@
         <v>44818</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77253,7 +77253,7 @@
         <v>45673</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77326,7 +77326,7 @@
         <v>44831</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77399,7 +77399,7 @@
         <v>45001</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77477,7 +77477,7 @@
         <v>45254</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77555,7 +77555,7 @@
         <v>45090</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77628,7 +77628,7 @@
         <v>45132</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77701,7 +77701,7 @@
         <v>45335</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77774,7 +77774,7 @@
         <v>45602</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77847,7 +77847,7 @@
         <v>44963</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77920,7 +77920,7 @@
         <v>45168</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77993,7 +77993,7 @@
         <v>45400</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78066,7 +78066,7 @@
         <v>45188</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78139,7 +78139,7 @@
         <v>45670</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78212,7 +78212,7 @@
         <v>44902</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78285,7 +78285,7 @@
         <v>44564</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78363,7 +78363,7 @@
         <v>45189</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78441,7 +78441,7 @@
         <v>45691</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78514,7 +78514,7 @@
         <v>44916</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78587,7 +78587,7 @@
         <v>44957</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78660,7 +78660,7 @@
         <v>44502</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78733,7 +78733,7 @@
         <v>45702</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78811,7 +78811,7 @@
         <v>44431</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78884,7 +78884,7 @@
         <v>45134</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78957,7 +78957,7 @@
         <v>45348</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79030,7 +79030,7 @@
         <v>45439</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79103,7 +79103,7 @@
         <v>44781</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79176,7 +79176,7 @@
         <v>45783</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79249,7 +79249,7 @@
         <v>45783</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79322,7 +79322,7 @@
         <v>45439</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79395,7 +79395,7 @@
         <v>44592</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79468,7 +79468,7 @@
         <v>45786</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79541,7 +79541,7 @@
         <v>45601</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79614,7 +79614,7 @@
         <v>45456</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79687,7 +79687,7 @@
         <v>45716</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79760,7 +79760,7 @@
         <v>45792</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79833,7 +79833,7 @@
         <v>45741</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79911,7 +79911,7 @@
         <v>45741</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79989,7 +79989,7 @@
         <v>45728</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80062,7 +80062,7 @@
         <v>45259</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80135,7 +80135,7 @@
         <v>45610</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80208,7 +80208,7 @@
         <v>45743</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80281,7 +80281,7 @@
         <v>45737</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80354,7 +80354,7 @@
         <v>45737</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80427,7 +80427,7 @@
         <v>45742</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80500,7 +80500,7 @@
         <v>45733</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80573,7 +80573,7 @@
         <v>45733</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80646,7 +80646,7 @@
         <v>45803</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80719,7 +80719,7 @@
         <v>45743</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80792,7 +80792,7 @@
         <v>45442</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80865,7 +80865,7 @@
         <v>45708</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80938,7 +80938,7 @@
         <v>45616</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81011,7 +81011,7 @@
         <v>45359</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81084,7 +81084,7 @@
         <v>45805</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81157,7 +81157,7 @@
         <v>45434</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81230,7 +81230,7 @@
         <v>45811</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81303,7 +81303,7 @@
         <v>45615</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81376,7 +81376,7 @@
         <v>45505</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81449,7 +81449,7 @@
         <v>45812</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81522,7 +81522,7 @@
         <v>45816</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81595,7 +81595,7 @@
         <v>45819</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81668,7 +81668,7 @@
         <v>45819</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81741,7 +81741,7 @@
         <v>45819</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81814,7 +81814,7 @@
         <v>45819</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81887,7 +81887,7 @@
         <v>45835</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81960,7 +81960,7 @@
         <v>45737</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82033,7 +82033,7 @@
         <v>45838</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82106,7 +82106,7 @@
         <v>45839</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82179,7 +82179,7 @@
         <v>45840</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82252,7 +82252,7 @@
         <v>45840</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82325,7 +82325,7 @@
         <v>45845</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82398,7 +82398,7 @@
         <v>45729</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82471,7 +82471,7 @@
         <v>45748</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82544,7 +82544,7 @@
         <v>45747</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82617,7 +82617,7 @@
         <v>45625</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82690,7 +82690,7 @@
         <v>45715</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82763,7 +82763,7 @@
         <v>45715</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82836,7 +82836,7 @@
         <v>44834</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82909,7 +82909,7 @@
         <v>45847</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -82982,7 +82982,7 @@
         <v>45763</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83055,7 +83055,7 @@
         <v>45852</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83128,7 +83128,7 @@
         <v>45672</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83201,7 +83201,7 @@
         <v>45163</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83274,7 +83274,7 @@
         <v>44549</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83347,7 +83347,7 @@
         <v>45322</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83420,7 +83420,7 @@
         <v>45005</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83493,7 +83493,7 @@
         <v>44564</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83566,7 +83566,7 @@
         <v>45866</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83639,7 +83639,7 @@
         <v>45288</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83712,7 +83712,7 @@
         <v>45733</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83785,7 +83785,7 @@
         <v>45113</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83858,7 +83858,7 @@
         <v>45636</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83931,7 +83931,7 @@
         <v>45580</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84004,7 +84004,7 @@
         <v>45447</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84077,7 +84077,7 @@
         <v>45170</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84150,7 +84150,7 @@
         <v>45106</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84223,7 +84223,7 @@
         <v>45467</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84296,7 +84296,7 @@
         <v>44509</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84374,7 +84374,7 @@
         <v>45664</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84447,7 +84447,7 @@
         <v>45208</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84520,7 +84520,7 @@
         <v>45406</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84593,7 +84593,7 @@
         <v>45497</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -84666,7 +84666,7 @@
         <v>45497</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -84739,7 +84739,7 @@
         <v>45106</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -84812,7 +84812,7 @@
         <v>45646</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84885,7 +84885,7 @@
         <v>44459</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84958,7 +84958,7 @@
         <v>45646</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -85031,7 +85031,7 @@
         <v>45580</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -85104,7 +85104,7 @@
         <v>45646</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -85177,7 +85177,7 @@
         <v>45646</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -85250,7 +85250,7 @@
         <v>45408</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -85323,7 +85323,7 @@
         <v>45414</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -85396,7 +85396,7 @@
         <v>45173</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -85469,7 +85469,7 @@
         <v>45646</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -85542,7 +85542,7 @@
         <v>45715</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -85615,7 +85615,7 @@
         <v>45720</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
@@ -85688,7 +85688,7 @@
         <v>45800</v>
       </c>
       <c r="E1103" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
@@ -85766,7 +85766,7 @@
         <v>45831</v>
       </c>
       <c r="E1104" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
@@ -85839,7 +85839,7 @@
         <v>45785</v>
       </c>
       <c r="E1105" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
@@ -85912,7 +85912,7 @@
         <v>46073</v>
       </c>
       <c r="E1106" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
@@ -85985,7 +85985,7 @@
         <v>46163</v>
       </c>
       <c r="E1107" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F1107" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>44890</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>44817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>45520</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45754</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>44612</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44908</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46100</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>45819</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>45477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>45583</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45763</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>45048</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44819</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45814</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>46045</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45599</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45035</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45357</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45400</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45310</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>44572</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>44468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>45211</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>45673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>46166</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45148</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>45303</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>45616</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>45891</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>45792</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>45835</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45840</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45860</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>45106</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>45509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45201</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>46051</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>44834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>44462</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44721</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44454</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>44747</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44592</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44740</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45378</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45342</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45021</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45835</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45119</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45672</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45775</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>45904</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45586</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45645</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>45239</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45085</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44781</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>46141</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44816</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45009</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45104</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>44728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45240</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45419</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>44880</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44819</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45930</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45337</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>46188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>46069</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>45565</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>46071</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>45596</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>45597</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45555</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45408</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>45532</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44998</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>45261</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44748</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>45643</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45352</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44434</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44830</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>45880</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45791</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>44916</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45736</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45820</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45839</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45713</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>45604</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45497</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>45614</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>44453</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>44426</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>44490</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>44438</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44838</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>44858</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>44781</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>44781</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>44732</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>44515</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44508</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>44579</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>44889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44601</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44504</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>44418</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44544</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>44441</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>44431</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44468</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44517</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44764</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44503</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44459</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44819</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44592</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44510</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44750</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>44825</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>44418</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>44460</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44424</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>44488</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44602</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>44638</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>44510</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>44721</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44785</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44587</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>44592</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44782</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44815</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>44432</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>44435</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44453</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44504</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44580</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44691</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>44880</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>44431</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>44460</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44435</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>44453</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>44434</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44545</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>44750</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>44462</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>44624</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>44446</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>44477</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>44595</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44608</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>44820</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>44454</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>44816</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>44460</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>44461</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>44645</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44819</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>44656</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>44784</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>44585</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>44585</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44585</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44834</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44740</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44440</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>44750</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>44587</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>44743</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44424</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44474</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44859</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44593</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>44743</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>44778</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44504</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44834</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>44477</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>44482</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44509</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44482</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>44488</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44462</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44564</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45763</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>44781</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45763</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45763</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>44592</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>44517</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>44502</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44572</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44721</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44841</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>44531</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45443</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45435</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>44888</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>44837</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>44636</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45449</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>44834</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44587</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>44655</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45446</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44461</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44454</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45330</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>44733</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>44683</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>44459</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44502</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45497</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45497</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>44515</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44592</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45544</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45546</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44463</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44957</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>44602</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>44792</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>44967</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44967</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44903</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45414</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45414</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44952</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44481</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44657</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>44858</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>44607</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>44827</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>44515</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44831</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45408</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>44434</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>44564</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45323</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>44880</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>45335</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>44834</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45329</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44998</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44592</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>44462</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45267</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>44531</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>45329</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45202</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>45302</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44825</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>45272</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>44946</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>45401</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>45300</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44683</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45345</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>44602</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45440</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45538</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>45884</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>44592</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45106</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45581</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44815</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>45364</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45201</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45414</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45211</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45097</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45091</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44600</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44459</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45357</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>44677</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>45170</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>45170</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45384</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>44587</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45884</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44902</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45674</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>44926</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>44926</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>45351</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45363</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>45363</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45420</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44929</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45107</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>45296</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44917</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45216</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45240</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44747</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>44902</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>44530</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44434</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44434</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45363</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>45363</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45742</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45190</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45561</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45370</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44813</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45492</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>45826</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>45441</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45394</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>45888</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45742</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45888</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45786</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45119</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45742</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45888</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45839</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>45541</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>45888</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>45462</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>45888</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45888</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45519</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>44837</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45341</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45532</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>45889</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>45677</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45461</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45440</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>45439</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44880</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>44880</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45889</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45889</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45691</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44946</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45309</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45363</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45770</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45839</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45623</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45033</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45022</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45563</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>45898</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>45785</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45706</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>45545</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44972</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44488</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45902</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45827</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>44600</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45819</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45737</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45663</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>45107</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44510</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45587</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45678</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>45840</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>45525</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>44715</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45162</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>45222</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>44641</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44965</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45691</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>44945</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44916</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45209</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>45911</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45911</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>44442</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45448</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>44916</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44916</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>44977</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45448</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44930</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45313</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45841</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45006</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>45006</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>45089</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>44952</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>45785</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>45589</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45589</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45062</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44984</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45183</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45922</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>45184</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45251</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44693</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45589</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>46122</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45925</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45281</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>45152</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>45351</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>45925</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45930</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45357</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>44480</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45930</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>45580</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>45931</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>44984</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>45307</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45936</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>44655</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45107</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>45936</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>45628</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45055</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45097</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45097</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>45525</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>44495</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45672</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45224</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45229</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>45097</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>45069</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>45669</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>45631</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45107</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45944</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>44470</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>44936</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45946</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>46153</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46196</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45219</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45950</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45615</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45183</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>44802</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45364</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44963</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>46153</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45135</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45219</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44930</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45282</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>46153</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>46153</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45015</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45245</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>46154</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>45163</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>44847</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>46196</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45310</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>46153</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>45953</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45953</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>46195</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45629</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45164</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45000</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>45763</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>44770</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>45574</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45575</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>45645</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>45645</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>44595</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>45362</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45251</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>45057</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45076</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45400</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45170</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>44783</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>44986</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45113</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>45114</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45631</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45692</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45639</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
         <v>46126</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45866</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45691</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>44582</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45709</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>46197</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>44839</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>44998</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>46197</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45644</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>44473</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45133</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45974</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45763</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45222</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45719</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>46064</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45761</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45930</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>46160</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44970</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>44815</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>46160</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>44894</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45434</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45302,7 +45302,7 @@
         <v>46160</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>46202</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45164</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>44810</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45594,7 +45594,7 @@
         <v>45205</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45975</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45071</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>44747</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>44434</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>46161</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
         <v>45274</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>44431</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45173</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45981</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45981</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>46160</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>45981</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45079</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46621,7 +46621,7 @@
         <v>45981</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45982</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46767,7 +46767,7 @@
         <v>46161</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>44740</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>44434</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45001</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>46204</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45702</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45572</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45091</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45329</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>45406</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47512,7 +47512,7 @@
         <v>45992</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45134</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45365</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45992</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45099</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>45462</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>44965</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45069</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>44916</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>45105</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45484</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>45992</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45992</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45992</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>45232</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>44818</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45082</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45568</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>44511</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>45538</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>44463</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45930</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49128,7 +49128,7 @@
         <v>44439</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49201,7 +49201,7 @@
         <v>45526</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49274,7 +49274,7 @@
         <v>44753</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>46163</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>45748</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45748</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>44869</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>45754</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>46168</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45999</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45999</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>44477</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45438</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45526</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>46001</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45406</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>45303</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>45104</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>44487</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45297</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50603,7 +50603,7 @@
         <v>45278</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>45771</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>45771</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50832,7 +50832,7 @@
         <v>45351</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>45250</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>46003</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51051,7 +51051,7 @@
         <v>45376</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>45099</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45226</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>45042</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45114</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51416,7 +51416,7 @@
         <v>45097</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51489,7 +51489,7 @@
         <v>46007</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>46007</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51635,7 +51635,7 @@
         <v>45769</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45104</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>45999</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51859,7 +51859,7 @@
         <v>45327</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51932,7 +51932,7 @@
         <v>45035</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>46010</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>46010</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>46009</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52224,7 +52224,7 @@
         <v>46009</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>45314</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52370,7 +52370,7 @@
         <v>46009</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52443,7 +52443,7 @@
         <v>46009</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45384</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45298</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52662,7 +52662,7 @@
         <v>45684</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>45660</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52813,7 +52813,7 @@
         <v>44946</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52886,7 +52886,7 @@
         <v>45182</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45182</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>45182</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45188</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>45089</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>45222</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>46213</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53407,7 +53407,7 @@
         <v>45827</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53480,7 +53480,7 @@
         <v>45089</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53553,7 +53553,7 @@
         <v>45602</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>45335</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>45336</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53772,7 +53772,7 @@
         <v>45701</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>45104</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>45104</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>46175</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45372</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>44447</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>46003</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>45231</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>46030</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>46030</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>45099</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>45580</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45330</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45254</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>46029</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54877,7 +54877,7 @@
         <v>45247</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>46031</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55023,7 +55023,7 @@
         <v>44460</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55096,7 +55096,7 @@
         <v>45265</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>46031</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>44831</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55315,7 +55315,7 @@
         <v>44510</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55388,7 +55388,7 @@
         <v>45331</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55461,7 +55461,7 @@
         <v>45575</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>46031</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>44462</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>45163</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55753,7 +55753,7 @@
         <v>45092</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45414</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55899,7 +55899,7 @@
         <v>45006</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55972,7 +55972,7 @@
         <v>44503</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56045,7 +56045,7 @@
         <v>45569</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45645</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45645</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>44984</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>44984</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56420,7 +56420,7 @@
         <v>45433</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56493,7 +56493,7 @@
         <v>44879</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>45462</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56639,7 +56639,7 @@
         <v>44859</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56712,7 +56712,7 @@
         <v>45455</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56785,7 +56785,7 @@
         <v>45030</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>45580</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56931,7 +56931,7 @@
         <v>45602</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57004,7 +57004,7 @@
         <v>44710</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57077,7 +57077,7 @@
         <v>45303</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>46177</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57223,7 +57223,7 @@
         <v>44995</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>46178</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>46178</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>46044</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45615</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57588,7 +57588,7 @@
         <v>45348</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57661,7 +57661,7 @@
         <v>46178</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57734,7 +57734,7 @@
         <v>45117</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57807,7 +57807,7 @@
         <v>45112</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57880,7 +57880,7 @@
         <v>45174</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>46178</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58031,7 +58031,7 @@
         <v>46178</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>46178</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>46178</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58250,7 +58250,7 @@
         <v>46048</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>46048</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>46045</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>45084</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58542,7 +58542,7 @@
         <v>46048</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58615,7 +58615,7 @@
         <v>46048</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58688,7 +58688,7 @@
         <v>44587</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58761,7 +58761,7 @@
         <v>46049</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58834,7 +58834,7 @@
         <v>45166</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>46178</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58980,7 +58980,7 @@
         <v>46178</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>45401</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45616</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59199,7 +59199,7 @@
         <v>44523</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>45048</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>46182</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59418,7 +59418,7 @@
         <v>45175</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59491,7 +59491,7 @@
         <v>46182</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>46055</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59637,7 +59637,7 @@
         <v>45401</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59710,7 +59710,7 @@
         <v>45168</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59783,7 +59783,7 @@
         <v>46184</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59856,7 +59856,7 @@
         <v>44545</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59929,7 +59929,7 @@
         <v>45161</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60002,7 +60002,7 @@
         <v>46182</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60075,7 +60075,7 @@
         <v>45133</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>46184</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>46184</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60294,7 +60294,7 @@
         <v>45113</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>45470</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>45182</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>46062</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>45321</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60659,7 +60659,7 @@
         <v>45478</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>45183</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60805,7 +60805,7 @@
         <v>45406</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>46185</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>45545</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>46062</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61097,7 +61097,7 @@
         <v>45569</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61170,7 +61170,7 @@
         <v>46063</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61243,7 +61243,7 @@
         <v>44743</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61316,7 +61316,7 @@
         <v>46063</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61389,7 +61389,7 @@
         <v>46063</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61462,7 +61462,7 @@
         <v>46063</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61535,7 +61535,7 @@
         <v>45132</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61608,7 +61608,7 @@
         <v>45649</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61686,7 +61686,7 @@
         <v>46185</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61759,7 +61759,7 @@
         <v>45540</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61832,7 +61832,7 @@
         <v>45350</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61905,7 +61905,7 @@
         <v>45525</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61978,7 +61978,7 @@
         <v>45031</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62051,7 +62051,7 @@
         <v>45341</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62124,7 +62124,7 @@
         <v>45168</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62197,7 +62197,7 @@
         <v>46188</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62270,7 +62270,7 @@
         <v>46069</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>45526</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45091</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         <v>45104</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62562,7 +62562,7 @@
         <v>45586</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>45170</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62708,7 +62708,7 @@
         <v>45170</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62781,7 +62781,7 @@
         <v>44592</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62854,7 +62854,7 @@
         <v>45673</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62927,7 +62927,7 @@
         <v>45701</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63005,7 +63005,7 @@
         <v>44459</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>44970</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63151,7 +63151,7 @@
         <v>45602</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63224,7 +63224,7 @@
         <v>45699</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63297,7 +63297,7 @@
         <v>46234</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63370,7 +63370,7 @@
         <v>44602</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63443,7 +63443,7 @@
         <v>44580</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63516,7 +63516,7 @@
         <v>46234</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63589,7 +63589,7 @@
         <v>46077</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63662,7 +63662,7 @@
         <v>44607</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63735,7 +63735,7 @@
         <v>46077</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63808,7 +63808,7 @@
         <v>45925</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63881,7 +63881,7 @@
         <v>45163</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63954,7 +63954,7 @@
         <v>46234</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64027,7 +64027,7 @@
         <v>46190</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64100,7 +64100,7 @@
         <v>45189</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64178,7 +64178,7 @@
         <v>45177</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64256,7 +64256,7 @@
         <v>46233</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64329,7 +64329,7 @@
         <v>45645</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64407,7 +64407,7 @@
         <v>45174</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64480,7 +64480,7 @@
         <v>45610</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64553,7 +64553,7 @@
         <v>45359</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64626,7 +64626,7 @@
         <v>45352</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64699,7 +64699,7 @@
         <v>46084</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64772,7 +64772,7 @@
         <v>45366</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64845,7 +64845,7 @@
         <v>46084</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64918,7 +64918,7 @@
         <v>45645</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64991,7 +64991,7 @@
         <v>46084</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65064,7 +65064,7 @@
         <v>44600</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65137,7 +65137,7 @@
         <v>45681</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45625</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65283,7 +65283,7 @@
         <v>46087</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65356,7 +65356,7 @@
         <v>45544</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65429,7 +65429,7 @@
         <v>44970</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65502,7 +65502,7 @@
         <v>45674</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65575,7 +65575,7 @@
         <v>45385</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65648,7 +65648,7 @@
         <v>46091</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65721,7 +65721,7 @@
         <v>46092</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65794,7 +65794,7 @@
         <v>46002</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65867,7 +65867,7 @@
         <v>45625</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65940,7 +65940,7 @@
         <v>46092</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66013,7 +66013,7 @@
         <v>45231</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66086,7 +66086,7 @@
         <v>45188</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66159,7 +66159,7 @@
         <v>45607</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66232,7 +66232,7 @@
         <v>45314</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66305,7 +66305,7 @@
         <v>45118</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66378,7 +66378,7 @@
         <v>45645</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66456,7 +66456,7 @@
         <v>45645</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66534,7 +66534,7 @@
         <v>46097</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66607,7 +66607,7 @@
         <v>45228</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66680,7 +66680,7 @@
         <v>45510</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66753,7 +66753,7 @@
         <v>46098</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66826,7 +66826,7 @@
         <v>45134</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66899,7 +66899,7 @@
         <v>46099</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66972,7 +66972,7 @@
         <v>45329</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67045,7 +67045,7 @@
         <v>45195</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67118,7 +67118,7 @@
         <v>45133</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67191,7 +67191,7 @@
         <v>45775</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67264,7 +67264,7 @@
         <v>45090</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67337,7 +67337,7 @@
         <v>45737</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67410,7 +67410,7 @@
         <v>46100</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67483,7 +67483,7 @@
         <v>45737</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67556,7 +67556,7 @@
         <v>45376</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67629,7 +67629,7 @@
         <v>45097</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67702,7 +67702,7 @@
         <v>45216</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67780,7 +67780,7 @@
         <v>46104</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67853,7 +67853,7 @@
         <v>45209</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67926,7 +67926,7 @@
         <v>46104</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67999,7 +67999,7 @@
         <v>45211</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68072,7 +68072,7 @@
         <v>45230</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>45561</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68223,7 +68223,7 @@
         <v>45113</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68296,7 +68296,7 @@
         <v>46104</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68369,7 +68369,7 @@
         <v>44655</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68442,7 +68442,7 @@
         <v>46107</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68515,7 +68515,7 @@
         <v>45572</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68588,7 +68588,7 @@
         <v>45702</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68666,7 +68666,7 @@
         <v>46107</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68739,7 +68739,7 @@
         <v>45398</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68812,7 +68812,7 @@
         <v>46107</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68885,7 +68885,7 @@
         <v>45446</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68958,7 +68958,7 @@
         <v>45392</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69031,7 +69031,7 @@
         <v>44888</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69104,7 +69104,7 @@
         <v>45315</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69177,7 +69177,7 @@
         <v>45202</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69250,7 +69250,7 @@
         <v>44949</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69323,7 +69323,7 @@
         <v>46111</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69396,7 +69396,7 @@
         <v>45236</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69469,7 +69469,7 @@
         <v>46111</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69542,7 +69542,7 @@
         <v>45230</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69620,7 +69620,7 @@
         <v>45173</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69693,7 +69693,7 @@
         <v>45173</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69766,7 +69766,7 @@
         <v>45595</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69839,7 +69839,7 @@
         <v>45670</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69912,7 +69912,7 @@
         <v>45274</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69985,7 +69985,7 @@
         <v>45180</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70058,7 +70058,7 @@
         <v>44781</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70131,7 +70131,7 @@
         <v>45439</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70204,7 +70204,7 @@
         <v>45188</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70277,7 +70277,7 @@
         <v>46121</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70350,7 +70350,7 @@
         <v>44762</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70423,7 +70423,7 @@
         <v>45348</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70496,7 +70496,7 @@
         <v>45400</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70569,7 +70569,7 @@
         <v>45191</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70642,7 +70642,7 @@
         <v>46121</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70715,7 +70715,7 @@
         <v>46122</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70788,7 +70788,7 @@
         <v>45188</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70861,7 +70861,7 @@
         <v>45204</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70934,7 +70934,7 @@
         <v>46126</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71007,7 +71007,7 @@
         <v>45238</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71085,7 +71085,7 @@
         <v>45135</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71158,7 +71158,7 @@
         <v>45135</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71231,7 +71231,7 @@
         <v>45135</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71304,7 +71304,7 @@
         <v>44462</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71377,7 +71377,7 @@
         <v>46127</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71450,7 +71450,7 @@
         <v>45259</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71523,7 +71523,7 @@
         <v>45322</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71596,7 +71596,7 @@
         <v>45783</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71669,7 +71669,7 @@
         <v>46128</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71742,7 +71742,7 @@
         <v>46128</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71815,7 +71815,7 @@
         <v>45783</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71888,7 +71888,7 @@
         <v>46128</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71961,7 +71961,7 @@
         <v>46128</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72034,7 +72034,7 @@
         <v>46128</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72107,7 +72107,7 @@
         <v>45135</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72180,7 +72180,7 @@
         <v>45716</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72253,7 +72253,7 @@
         <v>45456</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72326,7 +72326,7 @@
         <v>45319</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72399,7 +72399,7 @@
         <v>44592</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72472,7 +72472,7 @@
         <v>45245</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72545,7 +72545,7 @@
         <v>46133</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72618,7 +72618,7 @@
         <v>45439</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72691,7 +72691,7 @@
         <v>45754</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72769,7 +72769,7 @@
         <v>45754</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72847,7 +72847,7 @@
         <v>46133</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72920,7 +72920,7 @@
         <v>45307</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72993,7 +72993,7 @@
         <v>44741</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73066,7 +73066,7 @@
         <v>44813</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73139,7 +73139,7 @@
         <v>45719</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73212,7 +73212,7 @@
         <v>45671</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73285,7 +73285,7 @@
         <v>45331</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73358,7 +73358,7 @@
         <v>44970</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73431,7 +73431,7 @@
         <v>45357</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73504,7 +73504,7 @@
         <v>45309</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73577,7 +73577,7 @@
         <v>45352</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73650,7 +73650,7 @@
         <v>44830</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73723,7 +73723,7 @@
         <v>45786</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73796,7 +73796,7 @@
         <v>45309</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73869,7 +73869,7 @@
         <v>45309</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73942,7 +73942,7 @@
         <v>46006</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74015,7 +74015,7 @@
         <v>45153</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74088,7 +74088,7 @@
         <v>45891</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74161,7 +74161,7 @@
         <v>46037</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74234,7 +74234,7 @@
         <v>44839</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74307,7 +74307,7 @@
         <v>46112</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74385,7 +74385,7 @@
         <v>45306</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74458,7 +74458,7 @@
         <v>45883</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74531,7 +74531,7 @@
         <v>45895</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74604,7 +74604,7 @@
         <v>45912</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74677,7 +74677,7 @@
         <v>45944</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74750,7 +74750,7 @@
         <v>45755</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74823,7 +74823,7 @@
         <v>45250</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74896,7 +74896,7 @@
         <v>45314</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74969,7 +74969,7 @@
         <v>46136</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75042,7 +75042,7 @@
         <v>45309</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75115,7 +75115,7 @@
         <v>44805</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75188,7 +75188,7 @@
         <v>45699</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75261,7 +75261,7 @@
         <v>45601</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75334,7 +75334,7 @@
         <v>45889</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75407,7 +75407,7 @@
         <v>45076</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75480,7 +75480,7 @@
         <v>45902</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75553,7 +75553,7 @@
         <v>45971</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75626,7 +75626,7 @@
         <v>45007</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75699,7 +75699,7 @@
         <v>45348</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75772,7 +75772,7 @@
         <v>44792</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75845,7 +75845,7 @@
         <v>45303</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75918,7 +75918,7 @@
         <v>45365</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75991,7 +75991,7 @@
         <v>45608</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76064,7 +76064,7 @@
         <v>44481</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76137,7 +76137,7 @@
         <v>45825</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76210,7 +76210,7 @@
         <v>45971</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76283,7 +76283,7 @@
         <v>45610</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76356,7 +76356,7 @@
         <v>45302</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76429,7 +76429,7 @@
         <v>45264</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76502,7 +76502,7 @@
         <v>45264</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76575,7 +76575,7 @@
         <v>44538</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76648,7 +76648,7 @@
         <v>45112</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76721,7 +76721,7 @@
         <v>45330</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76794,7 +76794,7 @@
         <v>45903</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76867,7 +76867,7 @@
         <v>45839</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76940,7 +76940,7 @@
         <v>46052</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77013,7 +77013,7 @@
         <v>45799</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77086,7 +77086,7 @@
         <v>45827</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77159,7 +77159,7 @@
         <v>45670</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77232,7 +77232,7 @@
         <v>45931</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77305,7 +77305,7 @@
         <v>45965</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77378,7 +77378,7 @@
         <v>45839</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77451,7 +77451,7 @@
         <v>45866</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77524,7 +77524,7 @@
         <v>45873</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77597,7 +77597,7 @@
         <v>45883</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77670,7 +77670,7 @@
         <v>45693</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77743,7 +77743,7 @@
         <v>45763</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77816,7 +77816,7 @@
         <v>45925</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77889,7 +77889,7 @@
         <v>45351</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77962,7 +77962,7 @@
         <v>45272</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78035,7 +78035,7 @@
         <v>44785</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78108,7 +78108,7 @@
         <v>45792</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78181,7 +78181,7 @@
         <v>45071</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78254,7 +78254,7 @@
         <v>45645</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78327,7 +78327,7 @@
         <v>45370</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78400,7 +78400,7 @@
         <v>45645</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78478,7 +78478,7 @@
         <v>45259</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78551,7 +78551,7 @@
         <v>44888</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78624,7 +78624,7 @@
         <v>45595</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78697,7 +78697,7 @@
         <v>45674</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78770,7 +78770,7 @@
         <v>44448</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78848,7 +78848,7 @@
         <v>45316</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78921,7 +78921,7 @@
         <v>44971</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78994,7 +78994,7 @@
         <v>44851</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79067,7 +79067,7 @@
         <v>45475</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79140,7 +79140,7 @@
         <v>45743</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79213,7 +79213,7 @@
         <v>45733</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79286,7 +79286,7 @@
         <v>45733</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79359,7 +79359,7 @@
         <v>45737</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79432,7 +79432,7 @@
         <v>45737</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79505,7 +79505,7 @@
         <v>45329</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79578,7 +79578,7 @@
         <v>45329</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79651,7 +79651,7 @@
         <v>44965</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79724,7 +79724,7 @@
         <v>45742</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79797,7 +79797,7 @@
         <v>45728</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79870,7 +79870,7 @@
         <v>45741</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79948,7 +79948,7 @@
         <v>45741</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80026,7 +80026,7 @@
         <v>44497</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80099,7 +80099,7 @@
         <v>44484</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80172,7 +80172,7 @@
         <v>44916</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80245,7 +80245,7 @@
         <v>45259</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80318,7 +80318,7 @@
         <v>45610</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80391,7 +80391,7 @@
         <v>45708</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80464,7 +80464,7 @@
         <v>45442</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80537,7 +80537,7 @@
         <v>45743</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80610,7 +80610,7 @@
         <v>45803</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80683,7 +80683,7 @@
         <v>45616</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80756,7 +80756,7 @@
         <v>45359</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80829,7 +80829,7 @@
         <v>45805</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80902,7 +80902,7 @@
         <v>45505</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80975,7 +80975,7 @@
         <v>45434</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81048,7 +81048,7 @@
         <v>45615</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81121,7 +81121,7 @@
         <v>45812</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81194,7 +81194,7 @@
         <v>45811</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81267,7 +81267,7 @@
         <v>45816</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81340,7 +81340,7 @@
         <v>45819</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81413,7 +81413,7 @@
         <v>45819</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81486,7 +81486,7 @@
         <v>45819</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81559,7 +81559,7 @@
         <v>45819</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81632,7 +81632,7 @@
         <v>45737</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81705,7 +81705,7 @@
         <v>45838</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81778,7 +81778,7 @@
         <v>45840</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81851,7 +81851,7 @@
         <v>45840</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81924,7 +81924,7 @@
         <v>45839</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81997,7 +81997,7 @@
         <v>45625</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82070,7 +82070,7 @@
         <v>45715</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82143,7 +82143,7 @@
         <v>45747</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82216,7 +82216,7 @@
         <v>45729</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82289,7 +82289,7 @@
         <v>45845</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82362,7 +82362,7 @@
         <v>45715</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82435,7 +82435,7 @@
         <v>45748</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82508,7 +82508,7 @@
         <v>45847</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82581,7 +82581,7 @@
         <v>44834</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82654,7 +82654,7 @@
         <v>45852</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82727,7 +82727,7 @@
         <v>45763</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82800,7 +82800,7 @@
         <v>45322</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82873,7 +82873,7 @@
         <v>45005</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82946,7 +82946,7 @@
         <v>45163</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83019,7 +83019,7 @@
         <v>44549</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83092,7 +83092,7 @@
         <v>45672</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83165,7 +83165,7 @@
         <v>44564</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83238,7 +83238,7 @@
         <v>45733</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83311,7 +83311,7 @@
         <v>45113</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83384,7 +83384,7 @@
         <v>45866</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83457,7 +83457,7 @@
         <v>45288</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83530,7 +83530,7 @@
         <v>45874</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83603,7 +83603,7 @@
         <v>45875</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83676,7 +83676,7 @@
         <v>45875</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83749,7 +83749,7 @@
         <v>45875</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83822,7 +83822,7 @@
         <v>45882</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83895,7 +83895,7 @@
         <v>45882</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83968,7 +83968,7 @@
         <v>45636</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84041,7 +84041,7 @@
         <v>45580</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84114,7 +84114,7 @@
         <v>45447</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84187,7 +84187,7 @@
         <v>45170</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84260,7 +84260,7 @@
         <v>45106</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84333,7 +84333,7 @@
         <v>45467</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84406,7 +84406,7 @@
         <v>44509</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84484,7 +84484,7 @@
         <v>45664</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84557,7 +84557,7 @@
         <v>45208</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84630,7 +84630,7 @@
         <v>45406</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -84703,7 +84703,7 @@
         <v>45497</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -84776,7 +84776,7 @@
         <v>45497</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -84849,7 +84849,7 @@
         <v>45106</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84922,7 +84922,7 @@
         <v>45646</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84995,7 +84995,7 @@
         <v>44459</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -85068,7 +85068,7 @@
         <v>45646</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -85141,7 +85141,7 @@
         <v>45580</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -85214,7 +85214,7 @@
         <v>45646</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -85287,7 +85287,7 @@
         <v>45646</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -85360,7 +85360,7 @@
         <v>45408</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -85433,7 +85433,7 @@
         <v>45414</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -85506,7 +85506,7 @@
         <v>45173</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -85579,7 +85579,7 @@
         <v>45646</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -85652,7 +85652,7 @@
         <v>45715</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
@@ -85725,7 +85725,7 @@
         <v>45720</v>
       </c>
       <c r="E1103" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
@@ -85798,7 +85798,7 @@
         <v>45800</v>
       </c>
       <c r="E1104" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
@@ -85876,7 +85876,7 @@
         <v>45831</v>
       </c>
       <c r="E1105" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
@@ -85949,7 +85949,7 @@
         <v>45785</v>
       </c>
       <c r="E1106" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
@@ -86022,7 +86022,7 @@
         <v>46073</v>
       </c>
       <c r="E1107" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
@@ -86095,7 +86095,7 @@
         <v>46163</v>
       </c>
       <c r="E1108" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1108" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>44890</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>44817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>45520</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45754</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>44612</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44908</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46100</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>45819</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>45477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>45583</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45763</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>45048</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44819</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45814</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>46045</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45599</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45035</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45357</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>45400</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45310</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>44572</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>44468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>45211</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>45673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>46166</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45148</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>45303</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>45616</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>45891</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>45792</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>45835</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45840</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45860</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>45106</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>45509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45201</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>46051</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>44834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>44462</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44721</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44454</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>44747</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44592</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44740</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45378</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45342</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45021</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45835</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45119</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45672</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45775</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>45904</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45586</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45645</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>45239</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45085</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44781</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>46141</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44816</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45009</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45104</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>44728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45240</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45419</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>44880</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44819</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45930</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45337</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>46188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>46069</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>45565</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>46071</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>45596</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>45597</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45555</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45408</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>45532</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44998</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>45261</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44748</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>45643</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45352</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44434</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44830</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>45880</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45791</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>44916</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45736</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45820</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45839</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45713</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>45604</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45497</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>45614</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>44453</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>44426</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>44490</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>44438</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44838</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>44858</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>44781</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>44781</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>44732</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>44515</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44508</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>44579</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>44889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44601</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44504</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>44418</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44544</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>44441</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>44431</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44468</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44517</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44764</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44503</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44459</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44819</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44592</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44510</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44750</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>44825</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>44418</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>44460</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44424</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>44488</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44602</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>44638</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>44510</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>44721</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44785</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44587</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>44592</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44782</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44815</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>44432</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>44435</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44453</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44504</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44580</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44691</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>44880</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>44431</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>44460</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44435</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>44453</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>44434</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44545</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>44750</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>44462</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>44624</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>44446</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>44477</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>44595</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44608</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>44820</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>44454</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>44816</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>44460</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>44461</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>44645</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44819</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>44656</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>44784</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>44585</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>44585</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44585</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44834</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44740</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44440</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>44750</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>44587</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>44743</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44424</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44474</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44859</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44593</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>44743</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>44778</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44504</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44834</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>44477</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>44482</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44509</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44482</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>44488</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44462</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44564</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45763</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>44781</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45763</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45763</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>44592</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>44517</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>44502</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44572</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44721</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44841</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>44531</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45443</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45435</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>44888</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>44837</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>44636</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45449</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>44834</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44587</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>44655</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45446</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44461</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44454</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45330</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>44733</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>44683</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>44459</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44502</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45497</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45497</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>44515</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44592</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45544</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45546</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44463</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44957</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>44602</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>44792</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>44967</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44967</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44903</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45414</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45414</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44952</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44481</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44657</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>44858</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>44607</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>44827</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>44515</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44831</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45408</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>44434</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>44564</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45323</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>44880</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>45335</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>44834</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45329</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44998</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44592</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>44462</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45267</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>44531</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>45329</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45202</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>45302</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44825</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>45272</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>44946</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>45401</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>45300</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44683</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45345</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>44602</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45440</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45538</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>45884</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>44592</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45106</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45581</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44815</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>45364</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45201</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45414</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45211</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45097</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45091</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44600</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44459</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45357</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>44677</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>45170</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>45170</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45384</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>44587</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45884</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44902</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45674</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>44926</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>44926</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>45351</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45363</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>45363</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45420</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44929</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45107</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>45296</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44917</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45216</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45240</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44747</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>44902</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>44530</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44434</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44434</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45363</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>45363</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45742</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45190</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45561</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45370</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44813</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45492</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>45826</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>45441</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45394</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>45888</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45742</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45888</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45786</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45119</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45742</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45888</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45839</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>45541</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>45888</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>45462</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>45888</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45888</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45519</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>44837</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45341</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45532</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>45889</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>45677</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45461</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45440</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>45439</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44880</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>44880</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45889</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45889</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45691</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44946</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45309</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45363</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45770</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45839</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45623</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45033</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45022</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45563</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>45898</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>45785</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45706</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>45545</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44972</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44488</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45902</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45827</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>44600</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45819</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45737</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45663</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>45107</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44510</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45587</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45678</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>45840</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>45525</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>44715</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45162</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>45222</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>44641</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44965</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45691</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>44945</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44916</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45209</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>45911</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45911</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>44442</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45448</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>44916</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44916</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>44977</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45448</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44930</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45313</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45841</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45006</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>45006</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>45089</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>44952</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>45785</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>45589</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45589</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45062</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44984</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45183</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45922</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>45184</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45251</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44693</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45589</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>46122</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45925</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45281</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>45152</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>45351</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>45925</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45930</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45357</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>44480</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45930</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>45580</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>45931</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>44984</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>45307</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45936</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>44655</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45107</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>45936</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>45628</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45055</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45097</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45097</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>45525</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>44495</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45672</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45224</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45229</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>45097</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>45069</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>45669</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>45631</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45107</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45944</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>44470</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>44936</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45946</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>46153</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46196</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45219</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45950</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45615</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45183</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>44802</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45364</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44963</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>46153</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45135</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45219</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44930</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45282</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>46153</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>46153</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45015</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45245</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>46154</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>45163</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>44847</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>46196</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45310</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>46153</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>45953</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45953</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>46195</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45629</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45164</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45000</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>45763</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>44770</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>45574</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45575</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>45645</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>45645</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>44595</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>45362</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45251</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>45057</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45076</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45400</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45170</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>44783</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>44986</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45113</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>45114</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45631</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45692</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45639</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
         <v>46126</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45866</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45691</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>44582</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45709</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>46197</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>44839</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>44998</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>46197</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45644</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>44473</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45133</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45974</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45763</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45222</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45719</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>46064</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45761</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45930</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>46160</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44970</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>44815</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>46160</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>44894</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45434</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45302,7 +45302,7 @@
         <v>46160</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>46202</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45164</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>44810</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45594,7 +45594,7 @@
         <v>45205</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45975</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45071</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>44747</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>44434</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>46161</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
         <v>45274</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>44431</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45173</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45981</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45981</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>46160</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>45981</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45079</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46621,7 +46621,7 @@
         <v>45981</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45982</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46767,7 +46767,7 @@
         <v>46161</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>44740</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>44434</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45001</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>46204</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45702</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45572</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45091</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45329</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>45406</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47512,7 +47512,7 @@
         <v>45992</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45134</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45365</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45992</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45099</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>45462</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>44965</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45069</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>44916</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>45105</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45484</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>45992</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45992</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45992</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>45232</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>44818</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45082</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45568</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>44511</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>45538</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>44463</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45930</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49128,7 +49128,7 @@
         <v>44439</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49201,7 +49201,7 @@
         <v>45526</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49274,7 +49274,7 @@
         <v>44753</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>46163</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>45748</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45748</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>44869</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>45754</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>46168</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45999</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45999</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>44477</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45438</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45526</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>46001</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45406</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>45303</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>45104</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>44487</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45297</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50603,7 +50603,7 @@
         <v>45278</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>45771</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>45771</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50832,7 +50832,7 @@
         <v>45351</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>45250</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>46003</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51051,7 +51051,7 @@
         <v>45376</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>45099</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45226</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>45042</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45114</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51416,7 +51416,7 @@
         <v>45097</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51489,7 +51489,7 @@
         <v>46007</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>46007</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51635,7 +51635,7 @@
         <v>45769</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45104</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>45999</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51859,7 +51859,7 @@
         <v>45327</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51932,7 +51932,7 @@
         <v>45035</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>46010</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>46010</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>46009</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52224,7 +52224,7 @@
         <v>46009</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>45314</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52370,7 +52370,7 @@
         <v>46009</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52443,7 +52443,7 @@
         <v>46009</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45384</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45298</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52662,7 +52662,7 @@
         <v>45684</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>45660</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52813,7 +52813,7 @@
         <v>44946</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52886,7 +52886,7 @@
         <v>45182</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45182</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>45182</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45188</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>45089</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>45222</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>46213</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53407,7 +53407,7 @@
         <v>45827</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53480,7 +53480,7 @@
         <v>45089</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53553,7 +53553,7 @@
         <v>45602</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>45335</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>45336</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53772,7 +53772,7 @@
         <v>45701</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>45104</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>45104</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>46175</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45372</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>44447</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>46003</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>45231</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>46030</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>46030</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>45099</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>45580</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45330</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45254</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>46029</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54877,7 +54877,7 @@
         <v>45247</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>46031</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55023,7 +55023,7 @@
         <v>44460</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55096,7 +55096,7 @@
         <v>45265</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>46031</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>44831</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55315,7 +55315,7 @@
         <v>44510</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55388,7 +55388,7 @@
         <v>45331</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55461,7 +55461,7 @@
         <v>45575</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>46031</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>44462</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>45163</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55753,7 +55753,7 @@
         <v>45092</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45414</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55899,7 +55899,7 @@
         <v>45006</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55972,7 +55972,7 @@
         <v>44503</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56045,7 +56045,7 @@
         <v>45569</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45645</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45645</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>44984</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>44984</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56420,7 +56420,7 @@
         <v>45433</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56493,7 +56493,7 @@
         <v>44879</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>45462</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56639,7 +56639,7 @@
         <v>44859</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56712,7 +56712,7 @@
         <v>45455</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56785,7 +56785,7 @@
         <v>45030</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>45580</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56931,7 +56931,7 @@
         <v>45602</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57004,7 +57004,7 @@
         <v>44710</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57077,7 +57077,7 @@
         <v>45303</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>46177</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57223,7 +57223,7 @@
         <v>44995</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>46178</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>46178</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>46044</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45615</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57588,7 +57588,7 @@
         <v>45348</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57661,7 +57661,7 @@
         <v>46178</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57734,7 +57734,7 @@
         <v>45117</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57807,7 +57807,7 @@
         <v>45112</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57880,7 +57880,7 @@
         <v>45174</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>46178</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58031,7 +58031,7 @@
         <v>46178</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>46178</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>46178</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58250,7 +58250,7 @@
         <v>46048</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>46048</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>46045</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>45084</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58542,7 +58542,7 @@
         <v>46048</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58615,7 +58615,7 @@
         <v>46048</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58688,7 +58688,7 @@
         <v>44587</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58761,7 +58761,7 @@
         <v>46049</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58834,7 +58834,7 @@
         <v>45166</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>46178</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58980,7 +58980,7 @@
         <v>46178</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>45401</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45616</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59199,7 +59199,7 @@
         <v>44523</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>45048</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>46182</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59418,7 +59418,7 @@
         <v>45175</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59491,7 +59491,7 @@
         <v>46182</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>46055</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59637,7 +59637,7 @@
         <v>45401</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59710,7 +59710,7 @@
         <v>45168</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59783,7 +59783,7 @@
         <v>46184</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59856,7 +59856,7 @@
         <v>44545</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59929,7 +59929,7 @@
         <v>45161</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60002,7 +60002,7 @@
         <v>46182</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60075,7 +60075,7 @@
         <v>45133</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>46184</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>46184</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60294,7 +60294,7 @@
         <v>45113</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>45470</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>45182</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>46062</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>45321</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60659,7 +60659,7 @@
         <v>45478</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>45183</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60805,7 +60805,7 @@
         <v>45406</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>46185</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>45545</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>46062</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61097,7 +61097,7 @@
         <v>45569</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61170,7 +61170,7 @@
         <v>46063</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61243,7 +61243,7 @@
         <v>44743</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61316,7 +61316,7 @@
         <v>46063</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61389,7 +61389,7 @@
         <v>46063</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61462,7 +61462,7 @@
         <v>46063</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61535,7 +61535,7 @@
         <v>45132</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61608,7 +61608,7 @@
         <v>45649</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61686,7 +61686,7 @@
         <v>46185</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61759,7 +61759,7 @@
         <v>45540</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61832,7 +61832,7 @@
         <v>45350</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61905,7 +61905,7 @@
         <v>45525</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61978,7 +61978,7 @@
         <v>45031</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62051,7 +62051,7 @@
         <v>45341</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62124,7 +62124,7 @@
         <v>45168</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62197,7 +62197,7 @@
         <v>46188</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62270,7 +62270,7 @@
         <v>46069</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>45526</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45091</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         <v>45104</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62562,7 +62562,7 @@
         <v>45586</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>45170</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62708,7 +62708,7 @@
         <v>45170</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62781,7 +62781,7 @@
         <v>44592</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62854,7 +62854,7 @@
         <v>45673</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62927,7 +62927,7 @@
         <v>45701</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63005,7 +63005,7 @@
         <v>44459</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>44970</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63151,7 +63151,7 @@
         <v>45602</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63224,7 +63224,7 @@
         <v>45699</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63297,7 +63297,7 @@
         <v>46234</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63370,7 +63370,7 @@
         <v>44602</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63443,7 +63443,7 @@
         <v>44580</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63516,7 +63516,7 @@
         <v>46234</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63589,7 +63589,7 @@
         <v>46077</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63662,7 +63662,7 @@
         <v>44607</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63735,7 +63735,7 @@
         <v>46077</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63808,7 +63808,7 @@
         <v>45925</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63881,7 +63881,7 @@
         <v>45163</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63954,7 +63954,7 @@
         <v>46234</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64027,7 +64027,7 @@
         <v>46190</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64100,7 +64100,7 @@
         <v>45189</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64178,7 +64178,7 @@
         <v>45177</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64256,7 +64256,7 @@
         <v>46233</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64329,7 +64329,7 @@
         <v>45645</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64407,7 +64407,7 @@
         <v>45174</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64480,7 +64480,7 @@
         <v>45610</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64553,7 +64553,7 @@
         <v>45359</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64626,7 +64626,7 @@
         <v>45352</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64699,7 +64699,7 @@
         <v>46084</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64772,7 +64772,7 @@
         <v>45366</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64845,7 +64845,7 @@
         <v>46084</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64918,7 +64918,7 @@
         <v>45645</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64991,7 +64991,7 @@
         <v>46084</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65064,7 +65064,7 @@
         <v>44600</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65137,7 +65137,7 @@
         <v>45681</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45625</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65283,7 +65283,7 @@
         <v>46087</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65356,7 +65356,7 @@
         <v>45544</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65429,7 +65429,7 @@
         <v>44970</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65502,7 +65502,7 @@
         <v>45674</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65575,7 +65575,7 @@
         <v>45385</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65648,7 +65648,7 @@
         <v>46091</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65721,7 +65721,7 @@
         <v>46092</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65794,7 +65794,7 @@
         <v>46002</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65867,7 +65867,7 @@
         <v>45625</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65940,7 +65940,7 @@
         <v>46092</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66013,7 +66013,7 @@
         <v>45231</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66086,7 +66086,7 @@
         <v>45188</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66159,7 +66159,7 @@
         <v>45607</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66232,7 +66232,7 @@
         <v>45314</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66305,7 +66305,7 @@
         <v>45118</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66378,7 +66378,7 @@
         <v>45645</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66456,7 +66456,7 @@
         <v>45645</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66534,7 +66534,7 @@
         <v>46097</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66607,7 +66607,7 @@
         <v>45228</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66680,7 +66680,7 @@
         <v>45510</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66753,7 +66753,7 @@
         <v>46098</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66826,7 +66826,7 @@
         <v>45134</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66899,7 +66899,7 @@
         <v>46099</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66972,7 +66972,7 @@
         <v>45329</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67045,7 +67045,7 @@
         <v>45195</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67118,7 +67118,7 @@
         <v>45133</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67191,7 +67191,7 @@
         <v>45775</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67264,7 +67264,7 @@
         <v>45090</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67337,7 +67337,7 @@
         <v>45737</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67410,7 +67410,7 @@
         <v>46100</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67483,7 +67483,7 @@
         <v>45737</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67556,7 +67556,7 @@
         <v>45376</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67629,7 +67629,7 @@
         <v>45097</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67702,7 +67702,7 @@
         <v>45216</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67780,7 +67780,7 @@
         <v>46104</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67853,7 +67853,7 @@
         <v>45209</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67926,7 +67926,7 @@
         <v>46104</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67999,7 +67999,7 @@
         <v>45211</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68072,7 +68072,7 @@
         <v>45230</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>45561</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68223,7 +68223,7 @@
         <v>45113</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68296,7 +68296,7 @@
         <v>46104</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68369,7 +68369,7 @@
         <v>44655</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68442,7 +68442,7 @@
         <v>46107</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68515,7 +68515,7 @@
         <v>45572</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68588,7 +68588,7 @@
         <v>45702</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68666,7 +68666,7 @@
         <v>46107</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68739,7 +68739,7 @@
         <v>45398</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68812,7 +68812,7 @@
         <v>46107</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68885,7 +68885,7 @@
         <v>45446</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68958,7 +68958,7 @@
         <v>45392</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69031,7 +69031,7 @@
         <v>44888</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69104,7 +69104,7 @@
         <v>45315</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69177,7 +69177,7 @@
         <v>45202</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69250,7 +69250,7 @@
         <v>44949</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69323,7 +69323,7 @@
         <v>46111</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69396,7 +69396,7 @@
         <v>45236</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69469,7 +69469,7 @@
         <v>46111</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69542,7 +69542,7 @@
         <v>45230</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69620,7 +69620,7 @@
         <v>45173</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69693,7 +69693,7 @@
         <v>45173</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69766,7 +69766,7 @@
         <v>45595</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69839,7 +69839,7 @@
         <v>45670</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69912,7 +69912,7 @@
         <v>45274</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69985,7 +69985,7 @@
         <v>45180</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70058,7 +70058,7 @@
         <v>44781</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70131,7 +70131,7 @@
         <v>45439</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70204,7 +70204,7 @@
         <v>45188</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70277,7 +70277,7 @@
         <v>46121</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70350,7 +70350,7 @@
         <v>44762</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70423,7 +70423,7 @@
         <v>45348</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70496,7 +70496,7 @@
         <v>45400</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70569,7 +70569,7 @@
         <v>45191</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70642,7 +70642,7 @@
         <v>46121</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70715,7 +70715,7 @@
         <v>46122</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70788,7 +70788,7 @@
         <v>45188</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70861,7 +70861,7 @@
         <v>45204</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70934,7 +70934,7 @@
         <v>46126</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71007,7 +71007,7 @@
         <v>45238</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71085,7 +71085,7 @@
         <v>45135</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71158,7 +71158,7 @@
         <v>45135</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71231,7 +71231,7 @@
         <v>45135</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71304,7 +71304,7 @@
         <v>44462</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71377,7 +71377,7 @@
         <v>46127</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71450,7 +71450,7 @@
         <v>45259</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71523,7 +71523,7 @@
         <v>45322</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71596,7 +71596,7 @@
         <v>45783</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71669,7 +71669,7 @@
         <v>46128</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71742,7 +71742,7 @@
         <v>46128</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71815,7 +71815,7 @@
         <v>45783</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71888,7 +71888,7 @@
         <v>46128</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71961,7 +71961,7 @@
         <v>46128</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72034,7 +72034,7 @@
         <v>46128</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72107,7 +72107,7 @@
         <v>45135</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72180,7 +72180,7 @@
         <v>45716</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72253,7 +72253,7 @@
         <v>45456</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72326,7 +72326,7 @@
         <v>45319</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72399,7 +72399,7 @@
         <v>44592</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72472,7 +72472,7 @@
         <v>45245</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72545,7 +72545,7 @@
         <v>46133</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72618,7 +72618,7 @@
         <v>45439</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72691,7 +72691,7 @@
         <v>45754</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72769,7 +72769,7 @@
         <v>45754</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72847,7 +72847,7 @@
         <v>46133</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72920,7 +72920,7 @@
         <v>45307</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72993,7 +72993,7 @@
         <v>44741</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73066,7 +73066,7 @@
         <v>44813</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73139,7 +73139,7 @@
         <v>45719</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73212,7 +73212,7 @@
         <v>45671</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73285,7 +73285,7 @@
         <v>45331</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73358,7 +73358,7 @@
         <v>44970</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73431,7 +73431,7 @@
         <v>45357</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73504,7 +73504,7 @@
         <v>45309</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73577,7 +73577,7 @@
         <v>45352</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73650,7 +73650,7 @@
         <v>44830</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73723,7 +73723,7 @@
         <v>45786</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73796,7 +73796,7 @@
         <v>45309</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73869,7 +73869,7 @@
         <v>45309</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73942,7 +73942,7 @@
         <v>46006</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74015,7 +74015,7 @@
         <v>45153</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74088,7 +74088,7 @@
         <v>45891</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74161,7 +74161,7 @@
         <v>46037</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74234,7 +74234,7 @@
         <v>44839</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74307,7 +74307,7 @@
         <v>46112</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74385,7 +74385,7 @@
         <v>45306</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74458,7 +74458,7 @@
         <v>45883</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74531,7 +74531,7 @@
         <v>45895</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74604,7 +74604,7 @@
         <v>45912</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74677,7 +74677,7 @@
         <v>45944</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74750,7 +74750,7 @@
         <v>45755</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74823,7 +74823,7 @@
         <v>45250</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74896,7 +74896,7 @@
         <v>45314</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74969,7 +74969,7 @@
         <v>46136</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75042,7 +75042,7 @@
         <v>45309</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75115,7 +75115,7 @@
         <v>44805</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75188,7 +75188,7 @@
         <v>45699</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75261,7 +75261,7 @@
         <v>45601</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75334,7 +75334,7 @@
         <v>45889</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75407,7 +75407,7 @@
         <v>45076</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75480,7 +75480,7 @@
         <v>45902</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75553,7 +75553,7 @@
         <v>45971</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75626,7 +75626,7 @@
         <v>45007</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75699,7 +75699,7 @@
         <v>45348</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75772,7 +75772,7 @@
         <v>44792</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75845,7 +75845,7 @@
         <v>45303</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75918,7 +75918,7 @@
         <v>45365</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75991,7 +75991,7 @@
         <v>45608</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76064,7 +76064,7 @@
         <v>44481</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76137,7 +76137,7 @@
         <v>45825</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76210,7 +76210,7 @@
         <v>45971</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76283,7 +76283,7 @@
         <v>45610</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76356,7 +76356,7 @@
         <v>45302</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76429,7 +76429,7 @@
         <v>45264</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76502,7 +76502,7 @@
         <v>45264</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76575,7 +76575,7 @@
         <v>44538</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76648,7 +76648,7 @@
         <v>45112</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76721,7 +76721,7 @@
         <v>45330</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76794,7 +76794,7 @@
         <v>45903</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76867,7 +76867,7 @@
         <v>45839</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76940,7 +76940,7 @@
         <v>46052</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77013,7 +77013,7 @@
         <v>45799</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77086,7 +77086,7 @@
         <v>45827</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77159,7 +77159,7 @@
         <v>45670</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77232,7 +77232,7 @@
         <v>45931</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77305,7 +77305,7 @@
         <v>45965</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77378,7 +77378,7 @@
         <v>45839</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77451,7 +77451,7 @@
         <v>45866</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77524,7 +77524,7 @@
         <v>45873</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77597,7 +77597,7 @@
         <v>45883</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77670,7 +77670,7 @@
         <v>45693</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77743,7 +77743,7 @@
         <v>45763</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77816,7 +77816,7 @@
         <v>45925</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77889,7 +77889,7 @@
         <v>45351</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77962,7 +77962,7 @@
         <v>45272</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78035,7 +78035,7 @@
         <v>44785</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78108,7 +78108,7 @@
         <v>45792</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78181,7 +78181,7 @@
         <v>45071</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78254,7 +78254,7 @@
         <v>45645</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78327,7 +78327,7 @@
         <v>45370</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78400,7 +78400,7 @@
         <v>45645</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78478,7 +78478,7 @@
         <v>45259</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78551,7 +78551,7 @@
         <v>44888</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78624,7 +78624,7 @@
         <v>45595</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78697,7 +78697,7 @@
         <v>45674</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78770,7 +78770,7 @@
         <v>44448</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78848,7 +78848,7 @@
         <v>45316</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78921,7 +78921,7 @@
         <v>44971</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78994,7 +78994,7 @@
         <v>44851</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79067,7 +79067,7 @@
         <v>45475</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79140,7 +79140,7 @@
         <v>45743</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79213,7 +79213,7 @@
         <v>45733</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79286,7 +79286,7 @@
         <v>45733</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79359,7 +79359,7 @@
         <v>45737</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79432,7 +79432,7 @@
         <v>45737</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79505,7 +79505,7 @@
         <v>45329</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79578,7 +79578,7 @@
         <v>45329</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79651,7 +79651,7 @@
         <v>44965</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79724,7 +79724,7 @@
         <v>45742</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79797,7 +79797,7 @@
         <v>45728</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79870,7 +79870,7 @@
         <v>45741</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79948,7 +79948,7 @@
         <v>45741</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80026,7 +80026,7 @@
         <v>44497</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80099,7 +80099,7 @@
         <v>44484</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80172,7 +80172,7 @@
         <v>44916</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80245,7 +80245,7 @@
         <v>45259</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80318,7 +80318,7 @@
         <v>45610</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80391,7 +80391,7 @@
         <v>45708</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80464,7 +80464,7 @@
         <v>45442</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80537,7 +80537,7 @@
         <v>45743</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80610,7 +80610,7 @@
         <v>45803</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80683,7 +80683,7 @@
         <v>45616</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80756,7 +80756,7 @@
         <v>45359</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80829,7 +80829,7 @@
         <v>45805</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80902,7 +80902,7 @@
         <v>45505</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80975,7 +80975,7 @@
         <v>45434</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81048,7 +81048,7 @@
         <v>45615</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81121,7 +81121,7 @@
         <v>45812</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81194,7 +81194,7 @@
         <v>45811</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81267,7 +81267,7 @@
         <v>45816</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81340,7 +81340,7 @@
         <v>45819</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81413,7 +81413,7 @@
         <v>45819</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81486,7 +81486,7 @@
         <v>45819</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81559,7 +81559,7 @@
         <v>45819</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81632,7 +81632,7 @@
         <v>45737</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81705,7 +81705,7 @@
         <v>45838</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81778,7 +81778,7 @@
         <v>45840</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81851,7 +81851,7 @@
         <v>45840</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81924,7 +81924,7 @@
         <v>45839</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81997,7 +81997,7 @@
         <v>45625</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82070,7 +82070,7 @@
         <v>45715</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82143,7 +82143,7 @@
         <v>45747</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82216,7 +82216,7 @@
         <v>45729</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82289,7 +82289,7 @@
         <v>45845</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82362,7 +82362,7 @@
         <v>45715</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82435,7 +82435,7 @@
         <v>45748</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82508,7 +82508,7 @@
         <v>45847</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82581,7 +82581,7 @@
         <v>44834</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82654,7 +82654,7 @@
         <v>45852</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82727,7 +82727,7 @@
         <v>45763</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82800,7 +82800,7 @@
         <v>45322</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82873,7 +82873,7 @@
         <v>45005</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82946,7 +82946,7 @@
         <v>45163</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83019,7 +83019,7 @@
         <v>44549</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83092,7 +83092,7 @@
         <v>45672</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83165,7 +83165,7 @@
         <v>44564</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83238,7 +83238,7 @@
         <v>45733</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83311,7 +83311,7 @@
         <v>45113</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83384,7 +83384,7 @@
         <v>45866</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83457,7 +83457,7 @@
         <v>45288</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83530,7 +83530,7 @@
         <v>45874</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83603,7 +83603,7 @@
         <v>45875</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83676,7 +83676,7 @@
         <v>45875</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83749,7 +83749,7 @@
         <v>45875</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83822,7 +83822,7 @@
         <v>45882</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83895,7 +83895,7 @@
         <v>45882</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83968,7 +83968,7 @@
         <v>45636</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84041,7 +84041,7 @@
         <v>45580</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84114,7 +84114,7 @@
         <v>45447</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84187,7 +84187,7 @@
         <v>45170</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84260,7 +84260,7 @@
         <v>45106</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84333,7 +84333,7 @@
         <v>45467</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84406,7 +84406,7 @@
         <v>44509</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84484,7 +84484,7 @@
         <v>45664</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84557,7 +84557,7 @@
         <v>45208</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84630,7 +84630,7 @@
         <v>45406</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -84703,7 +84703,7 @@
         <v>45497</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -84776,7 +84776,7 @@
         <v>45497</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -84849,7 +84849,7 @@
         <v>45106</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84922,7 +84922,7 @@
         <v>45646</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84995,7 +84995,7 @@
         <v>44459</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -85068,7 +85068,7 @@
         <v>45646</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -85141,7 +85141,7 @@
         <v>45580</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -85214,7 +85214,7 @@
         <v>45646</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -85287,7 +85287,7 @@
         <v>45646</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -85360,7 +85360,7 @@
         <v>45408</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -85433,7 +85433,7 @@
         <v>45414</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -85506,7 +85506,7 @@
         <v>45173</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -85579,7 +85579,7 @@
         <v>45646</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -85652,7 +85652,7 @@
         <v>45715</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
@@ -85725,7 +85725,7 @@
         <v>45720</v>
       </c>
       <c r="E1103" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
@@ -85798,7 +85798,7 @@
         <v>45800</v>
       </c>
       <c r="E1104" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
@@ -85876,7 +85876,7 @@
         <v>45831</v>
       </c>
       <c r="E1105" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
@@ -85949,7 +85949,7 @@
         <v>45785</v>
       </c>
       <c r="E1106" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
@@ -86022,7 +86022,7 @@
         <v>46073</v>
       </c>
       <c r="E1107" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
@@ -86095,7 +86095,7 @@
         <v>46163</v>
       </c>
       <c r="E1108" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F1108" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44890</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>44817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45520</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45930</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45754</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>44612</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>44908</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>44840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45819</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45763</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45477</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45599</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45048</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>44819</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45583</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45814</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>45400</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45965</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>45310</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>45035</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45357</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45792</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45835</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>44572</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>45840</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45589</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45860</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44468</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>45148</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45303</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>45891</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45211</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>45673</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>46166</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45106</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>45509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>45201</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>45539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>46051</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44462</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>44721</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44747</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44454</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>44592</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44740</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45378</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>45342</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45643</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45352</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45119</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>45835</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45672</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>45791</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45904</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45645</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45736</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45021</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45586</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45839</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>45085</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>45713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44781</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>44816</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>45009</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45240</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45419</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>44880</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>46069</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>46071</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45565</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>45596</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>45597</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45555</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>45408</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>45261</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45880</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44748</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>44830</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45775</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>44916</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>45239</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>46141</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>45104</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>44728</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>44819</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>45337</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45532</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>44998</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>46188</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45930</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>46248</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>45604</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45497</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45614</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44453</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44490</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44438</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44858</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44781</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>44732</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44838</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44515</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44508</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44504</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>44496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>44889</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>44579</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44601</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>44544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>44441</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>44510</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>44468</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44517</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>44764</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>44510</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>44503</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>44459</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44819</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44592</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>44750</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>44825</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44460</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44488</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>44602</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>44638</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>44721</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44510</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44785</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>44592</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44587</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44782</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44815</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44453</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44504</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44580</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44691</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44880</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44460</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44453</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44462</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44545</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44750</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44624</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44446</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44477</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44595</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>44608</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>44454</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44820</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>44460</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>44816</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44461</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44819</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44656</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>44784</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44585</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>44585</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>44585</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44834</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44750</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44440</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44740</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>44587</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>44743</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>44474</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44600</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44859</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44593</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>44743</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>44778</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44504</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>44477</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44482</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>44509</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>44834</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44592</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>44517</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44572</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44721</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>44841</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44888</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>44587</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>44655</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>44461</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>44454</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44459</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44502</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>44515</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>44592</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>44462</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44564</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>44781</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44531</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>44636</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44834</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>44733</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>44683</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>44463</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44602</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44792</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>44827</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45323</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44657</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45329</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45335</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44834</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>44825</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45272</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>45267</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>45401</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>45329</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45300</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>45345</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>45202</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>44815</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45364</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45091</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45348</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45414</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45211</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45097</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45384</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45884</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45783</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45953</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45953</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45201</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>44929</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45783</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>45107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45296</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45716</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45456</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>44592</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45240</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45439</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>44902</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45884</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>44530</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45786</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45370</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>44813</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45601</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45394</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45119</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45826</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>44837</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45888</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45532</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45742</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45888</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45786</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45461</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45440</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>45439</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45742</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>45888</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>45839</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>44880</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>44880</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45541</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45888</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>45309</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45363</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45888</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>45888</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45341</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45889</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45677</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45792</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45889</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45889</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44482</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45770</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>45839</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>45623</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45763</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45763</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45763</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45898</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45443</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45435</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44837</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45974</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45449</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>45902</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45819</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45737</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45446</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45330</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>45587</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>45497</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>45497</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         <v>45544</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>45546</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>44481</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>44858</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>44515</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>45743</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45911</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45911</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45733</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>45733</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45737</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>45737</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44564</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45742</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45728</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>45975</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>45741</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>45741</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44531</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45922</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44602</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45538</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>45259</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>45610</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>44592</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>45106</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>45581</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45925</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>45708</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>45442</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>45743</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45803</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>45616</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45359</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45805</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>45981</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>45981</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>45505</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45434</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45981</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45925</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>44600</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45981</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45982</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45357</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>45615</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45170</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45170</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>44587</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44902</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>44926</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44926</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>45420</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>45931</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>45812</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45936</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45811</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45216</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>45936</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45816</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45742</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>45561</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>45992</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33467,7 +33467,7 @@
         <v>45492</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>45992</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>45992</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>45992</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>45462</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33832,7 +33832,7 @@
         <v>45819</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>45819</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>45519</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>45819</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45819</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>45944</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>45691</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44946</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>45946</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45033</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>45022</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>45999</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45999</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45950</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>45563</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>45706</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45545</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>46001</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44600</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45663</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45107</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45678</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>44715</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45162</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45222</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>44641</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>44965</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>46003</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>45737</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44945</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>45838</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44916</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>45209</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>44442</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45448</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>44916</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>44916</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>44977</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>45448</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45840</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45840</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45839</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>44930</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45006</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45006</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45089</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45589</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>45589</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>45625</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45062</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45715</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37560,7 +37560,7 @@
         <v>45747</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45729</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>45845</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>45183</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>45715</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45748</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45184</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45251</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38144,7 +38144,7 @@
         <v>45847</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44834</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44693</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38363,7 +38363,7 @@
         <v>45852</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38436,7 +38436,7 @@
         <v>45763</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45281</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38582,7 +38582,7 @@
         <v>45351</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>45357</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45322</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38801,7 +38801,7 @@
         <v>45005</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38874,7 +38874,7 @@
         <v>45163</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>44549</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>45580</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39093,7 +39093,7 @@
         <v>45672</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44564</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>44984</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>45733</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>45113</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45866</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39531,7 +39531,7 @@
         <v>45288</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45307</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>46007</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>46007</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39823,7 +39823,7 @@
         <v>45107</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45875</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>45875</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45628</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>45875</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45097</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45097</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45525</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45672</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45882</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45882</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>45229</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45631</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44936</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>45999</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>44462</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>44802</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45015</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45163</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45629</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45164</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45000</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44770</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>46010</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>46010</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>46009</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>46009</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45645</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45645</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>44595</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>45076</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45170</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>44783</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44986</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45113</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45114</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>45631</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>45692</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>45691</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44582</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>45709</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>44839</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42904,7 +42904,7 @@
         <v>45644</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>44473</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>46009</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>46009</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43196,7 +43196,7 @@
         <v>45133</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>45763</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>45222</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43415,7 +43415,7 @@
         <v>45719</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45827</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43561,7 +43561,7 @@
         <v>44815</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>44894</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45434</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43780,7 +43780,7 @@
         <v>44810</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>45205</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45071</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43999,7 +43999,7 @@
         <v>46003</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>45274</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45173</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>45079</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>44740</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>45001</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45702</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         <v>46030</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>46030</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44666,7 +44666,7 @@
         <v>45572</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>46029</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>46031</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>46031</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>46031</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45031,7 +45031,7 @@
         <v>45069</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>44916</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45177,7 +45177,7 @@
         <v>45105</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>45232</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>44818</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45396,7 +45396,7 @@
         <v>45082</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>46044</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45568</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>44511</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45538</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>44463</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>44439</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>44753</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>45748</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46063,7 +46063,7 @@
         <v>45748</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>44869</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46214,7 +46214,7 @@
         <v>46048</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>46048</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>45754</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>46045</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>46048</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>44477</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
         <v>46048</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45438</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>45526</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46876,7 +46876,7 @@
         <v>45406</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>46049</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>45104</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>44487</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45297</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45278</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>45771</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45771</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45351</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47543,7 +47543,7 @@
         <v>45250</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47616,7 +47616,7 @@
         <v>45376</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47689,7 +47689,7 @@
         <v>45099</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>46055</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47835,7 +47835,7 @@
         <v>45097</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45769</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47986,7 +47986,7 @@
         <v>45104</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45133</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45314</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>45384</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48278,7 +48278,7 @@
         <v>44946</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45089</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45336</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48497,7 +48497,7 @@
         <v>46062</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48570,7 +48570,7 @@
         <v>45701</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45104</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45104</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45372</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48867,7 +48867,7 @@
         <v>45231</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>46062</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>45099</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49086,7 +49086,7 @@
         <v>45580</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45330</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45254</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>45247</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>44460</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>45265</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49529,7 +49529,7 @@
         <v>44831</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49602,7 +49602,7 @@
         <v>44510</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45331</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49748,7 +49748,7 @@
         <v>45575</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>44462</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>45163</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>45092</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45414</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>45006</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         <v>44503</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50259,7 +50259,7 @@
         <v>45569</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>46063</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>44984</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>44984</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45433</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>44879</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45462</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50775,7 +50775,7 @@
         <v>44859</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>45455</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45030</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50994,7 +50994,7 @@
         <v>45602</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>45303</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>46063</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51213,7 +51213,7 @@
         <v>46063</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>46063</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>44995</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>45615</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>45348</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51578,7 +51578,7 @@
         <v>45117</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51651,7 +51651,7 @@
         <v>45112</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45174</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51802,7 +51802,7 @@
         <v>45084</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>44587</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45166</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52021,7 +52021,7 @@
         <v>45401</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45616</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52167,7 +52167,7 @@
         <v>44523</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>45048</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52313,7 +52313,7 @@
         <v>45175</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52386,7 +52386,7 @@
         <v>46077</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>46077</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45401</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>45168</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>44545</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52751,7 +52751,7 @@
         <v>45161</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52824,7 +52824,7 @@
         <v>45113</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>45470</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52970,7 +52970,7 @@
         <v>45182</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53043,7 +53043,7 @@
         <v>46084</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53116,7 +53116,7 @@
         <v>46084</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53189,7 +53189,7 @@
         <v>45478</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>46084</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53335,7 +53335,7 @@
         <v>45406</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45545</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>46087</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53554,7 +53554,7 @@
         <v>45569</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53627,7 +53627,7 @@
         <v>45540</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45350</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53773,7 +53773,7 @@
         <v>45525</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45031</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>45341</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>45168</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45091</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54138,7 +54138,7 @@
         <v>45104</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54211,7 +54211,7 @@
         <v>45586</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
         <v>45170</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>45170</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>44592</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54503,7 +54503,7 @@
         <v>45602</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54576,7 +54576,7 @@
         <v>45699</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54649,7 +54649,7 @@
         <v>46091</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>44602</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54795,7 +54795,7 @@
         <v>46092</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54868,7 +54868,7 @@
         <v>44580</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54941,7 +54941,7 @@
         <v>46002</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55014,7 +55014,7 @@
         <v>46092</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>44607</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55160,7 +55160,7 @@
         <v>45163</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55233,7 +55233,7 @@
         <v>45189</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>45177</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>45645</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>46097</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45174</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55613,7 +55613,7 @@
         <v>45610</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55686,7 +55686,7 @@
         <v>46098</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55759,7 +55759,7 @@
         <v>46099</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         <v>45352</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>46100</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>45366</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56051,7 +56051,7 @@
         <v>45645</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56124,7 +56124,7 @@
         <v>44600</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>45681</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56270,7 +56270,7 @@
         <v>46104</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56343,7 +56343,7 @@
         <v>46104</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56416,7 +56416,7 @@
         <v>46104</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>46107</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56562,7 +56562,7 @@
         <v>46107</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56635,7 +56635,7 @@
         <v>46107</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56708,7 +56708,7 @@
         <v>46111</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56781,7 +56781,7 @@
         <v>46111</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56854,7 +56854,7 @@
         <v>45625</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56927,7 +56927,7 @@
         <v>45231</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57000,7 +57000,7 @@
         <v>45607</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57073,7 +57073,7 @@
         <v>46121</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45118</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>46121</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>46122</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57365,7 +57365,7 @@
         <v>45510</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>45134</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57511,7 +57511,7 @@
         <v>45195</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45133</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57657,7 +57657,7 @@
         <v>45775</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57730,7 +57730,7 @@
         <v>45090</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57803,7 +57803,7 @@
         <v>46126</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>44462</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>46127</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58022,7 +58022,7 @@
         <v>45097</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58095,7 +58095,7 @@
         <v>46128</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58168,7 +58168,7 @@
         <v>46128</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58241,7 +58241,7 @@
         <v>45216</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>46128</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>45209</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>46128</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         <v>45211</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58611,7 +58611,7 @@
         <v>46128</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45230</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58762,7 +58762,7 @@
         <v>45561</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58835,7 +58835,7 @@
         <v>45113</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>44655</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58981,7 +58981,7 @@
         <v>45572</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>46133</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59127,7 +59127,7 @@
         <v>45398</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59200,7 +59200,7 @@
         <v>45446</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59273,7 +59273,7 @@
         <v>46133</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59346,7 +59346,7 @@
         <v>45392</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59419,7 +59419,7 @@
         <v>44888</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45202</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>45236</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59638,7 +59638,7 @@
         <v>46006</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45153</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59784,7 +59784,7 @@
         <v>45891</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59857,7 +59857,7 @@
         <v>46037</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59930,7 +59930,7 @@
         <v>46112</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60008,7 +60008,7 @@
         <v>45173</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60081,7 +60081,7 @@
         <v>45173</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60154,7 +60154,7 @@
         <v>45306</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45883</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>45895</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45912</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>45944</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60519,7 +60519,7 @@
         <v>45755</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60592,7 +60592,7 @@
         <v>45180</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60665,7 +60665,7 @@
         <v>46136</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60738,7 +60738,7 @@
         <v>45699</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60811,7 +60811,7 @@
         <v>45188</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60884,7 +60884,7 @@
         <v>45889</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60957,7 +60957,7 @@
         <v>45902</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61030,7 +61030,7 @@
         <v>45971</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61103,7 +61103,7 @@
         <v>45348</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61176,7 +61176,7 @@
         <v>45608</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61249,7 +61249,7 @@
         <v>45825</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61322,7 +61322,7 @@
         <v>45971</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61395,7 +61395,7 @@
         <v>45610</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61468,7 +61468,7 @@
         <v>44538</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61541,7 +61541,7 @@
         <v>45112</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61614,7 +61614,7 @@
         <v>45903</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>44762</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>45839</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>46052</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>45799</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61979,7 +61979,7 @@
         <v>45827</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62052,7 +62052,7 @@
         <v>45670</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62125,7 +62125,7 @@
         <v>45931</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62198,7 +62198,7 @@
         <v>45400</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62271,7 +62271,7 @@
         <v>45965</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62344,7 +62344,7 @@
         <v>45839</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62417,7 +62417,7 @@
         <v>45191</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>45866</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62563,7 +62563,7 @@
         <v>45873</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45883</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62709,7 +62709,7 @@
         <v>45693</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62782,7 +62782,7 @@
         <v>45763</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62855,7 +62855,7 @@
         <v>45925</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62928,7 +62928,7 @@
         <v>45188</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63001,7 +63001,7 @@
         <v>45204</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63074,7 +63074,7 @@
         <v>45238</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63152,7 +63152,7 @@
         <v>45135</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63225,7 +63225,7 @@
         <v>45135</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63298,7 +63298,7 @@
         <v>45135</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63371,7 +63371,7 @@
         <v>44785</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63444,7 +63444,7 @@
         <v>45259</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>45322</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63590,7 +63590,7 @@
         <v>45135</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63663,7 +63663,7 @@
         <v>45319</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63736,7 +63736,7 @@
         <v>45245</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63809,7 +63809,7 @@
         <v>45754</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63887,7 +63887,7 @@
         <v>45754</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63965,7 +63965,7 @@
         <v>45307</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64038,7 +64038,7 @@
         <v>44741</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64111,7 +64111,7 @@
         <v>45785</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64184,7 +64184,7 @@
         <v>44813</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>45719</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64330,7 +64330,7 @@
         <v>45671</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64403,7 +64403,7 @@
         <v>45331</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64476,7 +64476,7 @@
         <v>44970</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64549,7 +64549,7 @@
         <v>45357</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64622,7 +64622,7 @@
         <v>45309</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64695,7 +64695,7 @@
         <v>45352</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64768,7 +64768,7 @@
         <v>44830</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64841,7 +64841,7 @@
         <v>45309</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>45309</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64987,7 +64987,7 @@
         <v>44839</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65060,7 +65060,7 @@
         <v>45250</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65133,7 +65133,7 @@
         <v>45314</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65206,7 +65206,7 @@
         <v>45309</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65279,7 +65279,7 @@
         <v>44805</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65352,7 +65352,7 @@
         <v>45076</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65425,7 +65425,7 @@
         <v>45007</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65498,7 +65498,7 @@
         <v>44792</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65571,7 +65571,7 @@
         <v>45303</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65644,7 +65644,7 @@
         <v>45365</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65717,7 +65717,7 @@
         <v>44481</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65790,7 +65790,7 @@
         <v>45302</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65863,7 +65863,7 @@
         <v>45264</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65936,7 +65936,7 @@
         <v>45264</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66009,7 +66009,7 @@
         <v>45330</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66082,7 +66082,7 @@
         <v>45827</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66155,7 +66155,7 @@
         <v>44510</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66228,7 +66228,7 @@
         <v>45351</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66301,7 +66301,7 @@
         <v>45840</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66374,7 +66374,7 @@
         <v>45272</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66447,7 +66447,7 @@
         <v>45525</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66520,7 +66520,7 @@
         <v>45071</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66593,7 +66593,7 @@
         <v>45645</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66666,7 +66666,7 @@
         <v>45370</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66739,7 +66739,7 @@
         <v>45645</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66817,7 +66817,7 @@
         <v>45259</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66890,7 +66890,7 @@
         <v>44888</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66963,7 +66963,7 @@
         <v>45595</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67036,7 +67036,7 @@
         <v>45674</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67109,7 +67109,7 @@
         <v>44448</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67187,7 +67187,7 @@
         <v>45316</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67260,7 +67260,7 @@
         <v>44971</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67333,7 +67333,7 @@
         <v>44851</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67406,7 +67406,7 @@
         <v>45475</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67479,7 +67479,7 @@
         <v>45329</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67552,7 +67552,7 @@
         <v>45329</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67625,7 +67625,7 @@
         <v>44965</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67698,7 +67698,7 @@
         <v>44497</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67771,7 +67771,7 @@
         <v>44484</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67844,7 +67844,7 @@
         <v>44916</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67917,7 +67917,7 @@
         <v>44488</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67990,7 +67990,7 @@
         <v>44502</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68063,7 +68063,7 @@
         <v>45691</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68141,7 +68141,7 @@
         <v>44957</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68214,7 +68214,7 @@
         <v>44967</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68287,7 +68287,7 @@
         <v>44967</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68360,7 +68360,7 @@
         <v>44903</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68433,7 +68433,7 @@
         <v>45414</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68511,7 +68511,7 @@
         <v>45414</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68584,7 +68584,7 @@
         <v>44952</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68657,7 +68657,7 @@
         <v>44607</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68730,7 +68730,7 @@
         <v>44831</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68803,7 +68803,7 @@
         <v>45408</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68876,7 +68876,7 @@
         <v>44880</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68949,7 +68949,7 @@
         <v>44998</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69022,7 +69022,7 @@
         <v>44592</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69095,7 +69095,7 @@
         <v>45302</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69168,7 +69168,7 @@
         <v>44946</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69241,7 +69241,7 @@
         <v>44683</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69314,7 +69314,7 @@
         <v>45440</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69387,7 +69387,7 @@
         <v>44459</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69460,7 +69460,7 @@
         <v>44677</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69533,7 +69533,7 @@
         <v>45674</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69606,7 +69606,7 @@
         <v>45351</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69679,7 +69679,7 @@
         <v>45363</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69757,7 +69757,7 @@
         <v>45363</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69835,7 +69835,7 @@
         <v>44917</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69908,7 +69908,7 @@
         <v>44747</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69981,7 +69981,7 @@
         <v>45363</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70059,7 +70059,7 @@
         <v>45363</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70137,7 +70137,7 @@
         <v>45190</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70210,7 +70210,7 @@
         <v>45441</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70283,7 +70283,7 @@
         <v>44972</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70356,7 +70356,7 @@
         <v>44488</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70429,7 +70429,7 @@
         <v>45313</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70502,7 +70502,7 @@
         <v>44952</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70575,7 +70575,7 @@
         <v>44984</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70648,7 +70648,7 @@
         <v>45152</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70721,7 +70721,7 @@
         <v>44480</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70794,7 +70794,7 @@
         <v>44655</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70867,7 +70867,7 @@
         <v>45055</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70940,7 +70940,7 @@
         <v>44495</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71013,7 +71013,7 @@
         <v>45224</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71091,7 +71091,7 @@
         <v>45097</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71164,7 +71164,7 @@
         <v>45069</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71237,7 +71237,7 @@
         <v>45669</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71310,7 +71310,7 @@
         <v>45107</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71383,7 +71383,7 @@
         <v>44470</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71456,7 +71456,7 @@
         <v>45219</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71529,7 +71529,7 @@
         <v>45615</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71602,7 +71602,7 @@
         <v>45183</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71675,7 +71675,7 @@
         <v>45364</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71748,7 +71748,7 @@
         <v>45841</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71821,7 +71821,7 @@
         <v>44963</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71894,7 +71894,7 @@
         <v>45135</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71967,7 +71967,7 @@
         <v>45219</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72045,7 +72045,7 @@
         <v>44930</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72118,7 +72118,7 @@
         <v>45282</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72191,7 +72191,7 @@
         <v>45245</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72264,7 +72264,7 @@
         <v>44847</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72337,7 +72337,7 @@
         <v>45310</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72410,7 +72410,7 @@
         <v>45763</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72483,7 +72483,7 @@
         <v>45574</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72561,7 +72561,7 @@
         <v>45575</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72634,7 +72634,7 @@
         <v>45362</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72707,7 +72707,7 @@
         <v>45251</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72780,7 +72780,7 @@
         <v>45057</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72853,7 +72853,7 @@
         <v>44998</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72926,7 +72926,7 @@
         <v>44970</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72999,7 +72999,7 @@
         <v>45164</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73072,7 +73072,7 @@
         <v>44747</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73145,7 +73145,7 @@
         <v>45091</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73218,7 +73218,7 @@
         <v>45785</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73291,7 +73291,7 @@
         <v>45329</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73369,7 +73369,7 @@
         <v>45406</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73442,7 +73442,7 @@
         <v>45134</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73515,7 +73515,7 @@
         <v>45589</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73588,7 +73588,7 @@
         <v>46122</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73661,7 +73661,7 @@
         <v>45365</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73734,7 +73734,7 @@
         <v>45099</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73807,7 +73807,7 @@
         <v>45462</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73880,7 +73880,7 @@
         <v>44965</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73953,7 +73953,7 @@
         <v>45484</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74026,7 +74026,7 @@
         <v>45526</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74099,7 +74099,7 @@
         <v>45303</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74172,7 +74172,7 @@
         <v>45226</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74245,7 +74245,7 @@
         <v>45042</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74318,7 +74318,7 @@
         <v>45114</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74391,7 +74391,7 @@
         <v>45327</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74464,7 +74464,7 @@
         <v>45035</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74537,7 +74537,7 @@
         <v>45298</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74610,7 +74610,7 @@
         <v>45684</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74688,7 +74688,7 @@
         <v>45660</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74761,7 +74761,7 @@
         <v>45182</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74839,7 +74839,7 @@
         <v>45182</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74917,7 +74917,7 @@
         <v>45182</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74990,7 +74990,7 @@
         <v>45188</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75063,7 +75063,7 @@
         <v>45089</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75136,7 +75136,7 @@
         <v>45222</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75209,7 +75209,7 @@
         <v>45602</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75282,7 +75282,7 @@
         <v>45335</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75355,7 +75355,7 @@
         <v>44447</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75428,7 +75428,7 @@
         <v>45645</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75501,7 +75501,7 @@
         <v>45645</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75579,7 +75579,7 @@
         <v>45580</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75652,7 +75652,7 @@
         <v>44710</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75725,7 +75725,7 @@
         <v>45321</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75798,7 +75798,7 @@
         <v>45183</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75871,7 +75871,7 @@
         <v>44743</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75944,7 +75944,7 @@
         <v>45132</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76017,7 +76017,7 @@
         <v>45649</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76095,7 +76095,7 @@
         <v>45526</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76168,7 +76168,7 @@
         <v>45673</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76241,7 +76241,7 @@
         <v>45701</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76319,7 +76319,7 @@
         <v>44459</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76392,7 +76392,7 @@
         <v>44970</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76465,7 +76465,7 @@
         <v>46153</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76538,7 +76538,7 @@
         <v>45359</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76611,7 +76611,7 @@
         <v>46153</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76684,7 +76684,7 @@
         <v>45625</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76757,7 +76757,7 @@
         <v>46153</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76830,7 +76830,7 @@
         <v>46153</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76903,7 +76903,7 @@
         <v>45544</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76976,7 +76976,7 @@
         <v>46154</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77054,7 +77054,7 @@
         <v>46153</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77127,7 +77127,7 @@
         <v>44970</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77200,7 +77200,7 @@
         <v>45674</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77273,7 +77273,7 @@
         <v>45385</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77346,7 +77346,7 @@
         <v>45188</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77419,7 +77419,7 @@
         <v>45314</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77492,7 +77492,7 @@
         <v>45400</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77570,7 +77570,7 @@
         <v>45645</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77648,7 +77648,7 @@
         <v>45645</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77726,7 +77726,7 @@
         <v>45228</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77799,7 +77799,7 @@
         <v>45639</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77872,7 +77872,7 @@
         <v>46126</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77945,7 +77945,7 @@
         <v>45866</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78018,7 +78018,7 @@
         <v>45329</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78091,7 +78091,7 @@
         <v>45737</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78164,7 +78164,7 @@
         <v>45737</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78237,7 +78237,7 @@
         <v>45376</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78310,7 +78310,7 @@
         <v>45702</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78388,7 +78388,7 @@
         <v>45315</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78461,7 +78461,7 @@
         <v>44949</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78534,7 +78534,7 @@
         <v>45230</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78612,7 +78612,7 @@
         <v>45595</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78685,7 +78685,7 @@
         <v>45670</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78758,7 +78758,7 @@
         <v>45274</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78831,7 +78831,7 @@
         <v>44781</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78904,7 +78904,7 @@
         <v>45439</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78977,7 +78977,7 @@
         <v>46064</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79050,7 +79050,7 @@
         <v>45761</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79123,7 +79123,7 @@
         <v>45930</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79196,7 +79196,7 @@
         <v>46160</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79269,7 +79269,7 @@
         <v>46160</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79342,7 +79342,7 @@
         <v>46160</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79415,7 +79415,7 @@
         <v>46161</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79488,7 +79488,7 @@
         <v>46160</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79561,7 +79561,7 @@
         <v>46161</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79634,7 +79634,7 @@
         <v>45930</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79712,7 +79712,7 @@
         <v>46163</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79785,7 +79785,7 @@
         <v>46175</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79858,7 +79858,7 @@
         <v>46178</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79931,7 +79931,7 @@
         <v>46178</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80004,7 +80004,7 @@
         <v>46178</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80077,7 +80077,7 @@
         <v>46178</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80150,7 +80150,7 @@
         <v>46178</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80223,7 +80223,7 @@
         <v>46178</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80296,7 +80296,7 @@
         <v>46178</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80369,7 +80369,7 @@
         <v>46178</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80442,7 +80442,7 @@
         <v>46182</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80515,7 +80515,7 @@
         <v>46182</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80588,7 +80588,7 @@
         <v>46184</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80661,7 +80661,7 @@
         <v>46182</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80734,7 +80734,7 @@
         <v>46184</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80807,7 +80807,7 @@
         <v>46184</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80880,7 +80880,7 @@
         <v>46185</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80953,7 +80953,7 @@
         <v>46185</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81026,7 +81026,7 @@
         <v>46188</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81099,7 +81099,7 @@
         <v>46234</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81172,7 +81172,7 @@
         <v>46234</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81245,7 +81245,7 @@
         <v>45925</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81318,7 +81318,7 @@
         <v>46190</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81391,7 +81391,7 @@
         <v>46233</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81464,7 +81464,7 @@
         <v>46237</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81537,7 +81537,7 @@
         <v>46195</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81610,7 +81610,7 @@
         <v>46197</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81683,7 +81683,7 @@
         <v>46240</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81756,7 +81756,7 @@
         <v>46196</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81829,7 +81829,7 @@
         <v>46196</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81902,7 +81902,7 @@
         <v>46197</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81975,7 +81975,7 @@
         <v>46244</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82048,7 +82048,7 @@
         <v>46244</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82121,7 +82121,7 @@
         <v>46202</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82194,7 +82194,7 @@
         <v>46246</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82267,7 +82267,7 @@
         <v>46245</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82340,7 +82340,7 @@
         <v>46204</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82413,7 +82413,7 @@
         <v>46252</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82486,7 +82486,7 @@
         <v>46069</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82559,7 +82559,7 @@
         <v>46255</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82632,7 +82632,7 @@
         <v>46213</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82705,7 +82705,7 @@
         <v>46168</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82778,7 +82778,7 @@
         <v>46247</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82856,7 +82856,7 @@
         <v>46258</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82929,7 +82929,7 @@
         <v>46248</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83007,7 +83007,7 @@
         <v>46258</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83080,7 +83080,7 @@
         <v>46259</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83153,7 +83153,7 @@
         <v>46259</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83226,7 +83226,7 @@
         <v>46247</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83304,7 +83304,7 @@
         <v>46177</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83377,7 +83377,7 @@
         <v>46178</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83450,7 +83450,7 @@
         <v>46234</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83523,7 +83523,7 @@
         <v>45992</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83596,7 +83596,7 @@
         <v>45636</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83669,7 +83669,7 @@
         <v>45580</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83742,7 +83742,7 @@
         <v>45447</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83815,7 +83815,7 @@
         <v>45170</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83888,7 +83888,7 @@
         <v>45106</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83961,7 +83961,7 @@
         <v>45467</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84034,7 +84034,7 @@
         <v>44509</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84112,7 +84112,7 @@
         <v>45664</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84185,7 +84185,7 @@
         <v>45208</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84258,7 +84258,7 @@
         <v>45406</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84331,7 +84331,7 @@
         <v>45497</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84404,7 +84404,7 @@
         <v>45497</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84477,7 +84477,7 @@
         <v>45106</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84550,7 +84550,7 @@
         <v>45646</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84623,7 +84623,7 @@
         <v>44459</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -84696,7 +84696,7 @@
         <v>45646</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -84769,7 +84769,7 @@
         <v>45580</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -84842,7 +84842,7 @@
         <v>45646</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84915,7 +84915,7 @@
         <v>45646</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84988,7 +84988,7 @@
         <v>45408</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -85061,7 +85061,7 @@
         <v>45414</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -85134,7 +85134,7 @@
         <v>45173</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -85207,7 +85207,7 @@
         <v>45646</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -85280,7 +85280,7 @@
         <v>45715</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -85353,7 +85353,7 @@
         <v>45720</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -85426,7 +85426,7 @@
         <v>45800</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -85504,7 +85504,7 @@
         <v>45831</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -85577,7 +85577,7 @@
         <v>45785</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -85650,7 +85650,7 @@
         <v>46073</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
@@ -85723,7 +85723,7 @@
         <v>46163</v>
       </c>
       <c r="E1103" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F1103" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44817</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>44890</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45520</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45754</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>44612</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>44840</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44908</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>46100</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45819</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45583</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>46045</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>44819</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>45763</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45477</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45814</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45048</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>45589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>44468</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45792</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45835</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>45713</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>45840</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45860</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45673</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>45303</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>45148</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45891</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45357</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45616</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>46166</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45035</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45400</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45211</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>45310</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45106</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>45509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>45201</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>45539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>46051</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44462</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>44721</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44747</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44454</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>44592</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44740</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45597</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>44830</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>45596</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45736</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>45555</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45835</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45021</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45820</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>44748</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45904</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45645</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45839</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44824</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>45713</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45240</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44728</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45342</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>45586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>45672</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45239</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>46069</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>46071</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>44998</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44880</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>45419</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>45775</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45085</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45408</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45880</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44819</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45119</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>46141</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45009</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45261</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45378</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45104</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>44816</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45532</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>46188</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44833</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45337</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>44916</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45930</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>46248</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45352</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45643</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>45791</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>45604</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45497</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45614</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44453</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44490</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44858</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44838</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44781</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>44732</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44508</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>44889</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>44579</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>44544</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44601</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>44510</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>44468</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>44517</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>44764</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>44503</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>44819</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>44459</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>44592</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44750</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44825</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>44460</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>44488</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44638</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>44721</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>44510</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>44785</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44592</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44587</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>44782</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44815</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44453</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44504</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44580</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44691</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44880</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44460</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44453</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44545</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44750</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44462</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44624</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44446</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44477</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44595</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44608</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44454</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>44820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44460</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44816</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>44461</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>44645</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44819</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44656</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44784</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44585</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44585</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>44585</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44834</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>44740</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>44750</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44587</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>44743</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>44474</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>44600</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>44859</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>44593</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44743</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44778</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44504</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>44834</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>44482</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44509</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>44477</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44517</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>44592</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>44721</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44572</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>44841</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44888</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44587</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>44655</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44461</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>44454</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>44459</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>44515</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>44502</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44592</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>44462</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>44564</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>44781</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>44531</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44636</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>44834</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44733</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>44683</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44463</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>44602</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>44792</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>44657</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44827</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45561</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45251</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>44967</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44967</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44792</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>44592</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>45265</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>45267</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44880</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>45569</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>44902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45580</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44488</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>44903</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45674</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45175</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>44998</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45663</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45278</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45205</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45771</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45771</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45057</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45259</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>44477</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>45351</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45602</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>44582</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>44936</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>45264</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44831</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45091</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45188</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45307</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45575</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>44530</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
         <v>45350</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>45071</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45135</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>45229</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45055</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44600</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44851</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45406</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>44762</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>44710</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44986</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45384</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45434</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45439</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>44747</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45031</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45097</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45097</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45645</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45335</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>45104</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45300</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45709</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>45645</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>45099</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45309</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45309</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45470</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44949</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45097</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45272</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45309</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>44487</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45363</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45118</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45336</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45161</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45162</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45414</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45226</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>45188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44916</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44916</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45701</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45082</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45741</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45461</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45163</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45741</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45728</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45188</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>44655</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45259</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45580</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45610</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45743</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45737</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45737</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45341</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45742</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45191</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>44952</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>45733</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45733</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45209</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44888</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45803</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45743</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>45442</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>45708</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>45113</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>45616</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45839</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45359</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45754</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45754</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45351</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45628</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>44972</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45097</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45201</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45805</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44770</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45572</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>44916</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45884</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45434</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45190</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45811</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44592</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45448</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45166</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45615</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>45505</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45580</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>45625</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45362</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>46003</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44462</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45812</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45816</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>46029</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44977</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>45888</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>45888</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45541</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45677</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45545</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45889</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45786</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45819</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45888</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>45742</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45104</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45889</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45888</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45888</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45645</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45888</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45645</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>45754</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45826</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45889</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45742</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>45135</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45770</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>45819</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45135</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45135</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>45819</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45819</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>44641</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44482</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>45042</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45329</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>45586</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>45329</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45117</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45839</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>45623</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>44888</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45099</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45610</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45742</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44984</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>46031</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45898</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>45228</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45819</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45737</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45587</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45441</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45902</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>46031</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45274</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44693</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45595</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>46030</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45330</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>45202</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45702</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45376</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>46030</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45363</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>44916</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45911</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45911</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>44531</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>45737</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45365</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45414</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45838</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>46031</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45839</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45107</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37439,7 +37439,7 @@
         <v>45251</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>45319</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45922</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45840</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>44515</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>44984</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45840</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45232</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45462</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45845</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45925</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>44984</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38320,7 +38320,7 @@
         <v>44984</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>45357</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>45729</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>45748</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>45747</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>45048</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>45625</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>45715</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>45925</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>45715</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>44834</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>45581</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45847</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>44945</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45006</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45069</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45763</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>45931</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45484</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45852</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>45015</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>45310</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>45351</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>45170</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45672</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>45936</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>45163</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45936</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44549</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45322</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>45097</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45005</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>44564</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>45684</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45330</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>44946</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>45866</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>45107</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45288</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45733</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45099</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41323,7 +41323,7 @@
         <v>45113</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>45944</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>44460</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45352</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>45946</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>44837</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41761,7 +41761,7 @@
         <v>45875</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>45950</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45351</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45875</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45875</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45953</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>44484</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>45953</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45748</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>45748</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>46044</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>46045</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42647,7 +42647,7 @@
         <v>44965</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>46048</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>46048</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>46048</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>46049</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>46048</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45882</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45882</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45884</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>46055</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>44970</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45133</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         <v>45357</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45133</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45231</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>44545</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>45681</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>45152</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>44503</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45230</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>44480</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>44741</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>45272</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45084</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44600</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45331</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45331</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>45222</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>44970</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>45671</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45435</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>45230</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45204</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45455</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>45561</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>46062</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>46063</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45282</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45245</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>46062</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>46063</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>46063</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>46063</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>45631</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>45247</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45259</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>45370</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45322</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45974</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>45975</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45035</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>45645</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>45645</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45076</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>45006</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>44580</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45089</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>45981</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>44459</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>45981</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45615</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45981</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>45538</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>45298</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47344,7 +47344,7 @@
         <v>45982</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45981</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>46077</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47563,7 +47563,7 @@
         <v>45372</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45076</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>46077</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>44473</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47855,7 +47855,7 @@
         <v>45170</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45401</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44607</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>44837</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>44511</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45089</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45443</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48366,7 +48366,7 @@
         <v>45992</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45240</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>45992</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45168</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48658,7 +48658,7 @@
         <v>45992</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48731,7 +48731,7 @@
         <v>45321</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48804,7 +48804,7 @@
         <v>45992</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>44470</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48950,7 +48950,7 @@
         <v>45163</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49023,7 +49023,7 @@
         <v>44510</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>45999</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45999</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>45211</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45414</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         <v>44894</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49461,7 +49461,7 @@
         <v>45519</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45314</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>45433</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45097</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>46084</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45448</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>46084</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>46001</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>45645</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         <v>45645</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>46084</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45644</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>46003</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>45649</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>45114</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>44858</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>46009</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>45545</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>46007</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50863,7 +50863,7 @@
         <v>46007</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50936,7 +50936,7 @@
         <v>46009</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45250</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51082,7 +51082,7 @@
         <v>45224</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>45999</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>46009</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>46009</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>46010</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45645</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>46010</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45763</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>46087</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>45672</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>45264</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45827</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>46091</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52041,7 +52041,7 @@
         <v>45525</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52114,7 +52114,7 @@
         <v>44965</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>44926</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>44926</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45401</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>46092</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>46092</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>45392</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45394</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>46002</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>44602</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>46097</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>45007</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>46098</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>45568</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45297</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53214,7 +53214,7 @@
         <v>45236</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45625</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53360,7 +53360,7 @@
         <v>45105</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>46099</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>44859</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>46100</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>46104</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53725,7 +53725,7 @@
         <v>46104</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53798,7 +53798,7 @@
         <v>46104</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45674</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>44481</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54017,7 +54017,7 @@
         <v>46107</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54090,7 +54090,7 @@
         <v>46107</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54163,7 +54163,7 @@
         <v>44655</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>44970</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>45329</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54382,7 +54382,7 @@
         <v>46107</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54455,7 +54455,7 @@
         <v>44847</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54528,7 +54528,7 @@
         <v>46111</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54601,7 +54601,7 @@
         <v>45180</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45173</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45173</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54820,7 +54820,7 @@
         <v>46111</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45345</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54966,7 +54966,7 @@
         <v>45526</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55039,7 +55039,7 @@
         <v>45170</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>45170</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45303</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>45104</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>46121</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55404,7 +55404,7 @@
         <v>46122</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>46121</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>45113</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>44462</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45446</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45438</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55842,7 +55842,7 @@
         <v>46126</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>46128</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55988,7 +55988,7 @@
         <v>46128</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56061,7 +56061,7 @@
         <v>46128</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>46128</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56207,7 +56207,7 @@
         <v>46127</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>45182</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56358,7 +56358,7 @@
         <v>45182</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>46128</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>44607</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>46133</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56650,7 +56650,7 @@
         <v>46133</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>45669</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>45315</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>45462</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45449</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57015,7 +57015,7 @@
         <v>44463</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57088,7 +57088,7 @@
         <v>45327</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57161,7 +57161,7 @@
         <v>45164</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45330</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45903</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>44995</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57453,7 +57453,7 @@
         <v>45692</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>45839</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57599,7 +57599,7 @@
         <v>45699</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57672,7 +57672,7 @@
         <v>45827</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57745,7 +57745,7 @@
         <v>46037</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57818,7 +57818,7 @@
         <v>45944</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57891,7 +57891,7 @@
         <v>45112</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57964,7 +57964,7 @@
         <v>45106</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58037,7 +58037,7 @@
         <v>45574</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45616</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58188,7 +58188,7 @@
         <v>45891</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45313</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>45799</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45510</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45306</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45219</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>45274</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58704,7 +58704,7 @@
         <v>45250</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58777,7 +58777,7 @@
         <v>45931</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>44587</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58923,7 +58923,7 @@
         <v>44783</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>44510</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>45895</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>45883</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>44830</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45544</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59361,7 +59361,7 @@
         <v>45133</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59434,7 +59434,7 @@
         <v>45408</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59507,7 +59507,7 @@
         <v>44834</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59580,7 +59580,7 @@
         <v>45366</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59653,7 +59653,7 @@
         <v>44815</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59726,7 +59726,7 @@
         <v>45069</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>45440</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59872,7 +59872,7 @@
         <v>45902</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59945,7 +59945,7 @@
         <v>45701</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60023,7 +60023,7 @@
         <v>46112</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60101,7 +60101,7 @@
         <v>45965</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60174,7 +60174,7 @@
         <v>45302</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60247,7 +60247,7 @@
         <v>45615</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>45525</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60393,7 +60393,7 @@
         <v>45113</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45785</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60539,7 +60539,7 @@
         <v>45912</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60612,7 +60612,7 @@
         <v>44683</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60685,7 +60685,7 @@
         <v>45840</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60758,7 +60758,7 @@
         <v>45866</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>45546</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60904,7 +60904,7 @@
         <v>45925</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>45971</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>44839</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>44970</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45222</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>46006</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>45183</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>45763</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61488,7 +61488,7 @@
         <v>44965</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45000</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61634,7 +61634,7 @@
         <v>45183</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45706</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61780,7 +61780,7 @@
         <v>45693</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61853,7 +61853,7 @@
         <v>45889</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61926,7 +61926,7 @@
         <v>45785</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61999,7 +61999,7 @@
         <v>44839</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         <v>44753</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>45841</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>45135</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>46136</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45608</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62437,7 +62437,7 @@
         <v>45873</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>45971</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45610</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>46122</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45153</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>45755</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>45670</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62948,7 +62948,7 @@
         <v>45825</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45348</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63094,7 +63094,7 @@
         <v>45839</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63167,7 +63167,7 @@
         <v>44802</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63245,7 +63245,7 @@
         <v>44538</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63318,7 +63318,7 @@
         <v>45446</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63391,7 +63391,7 @@
         <v>44785</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>46052</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63537,7 +63537,7 @@
         <v>45883</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63610,7 +63610,7 @@
         <v>44929</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63683,7 +63683,7 @@
         <v>44743</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63756,7 +63756,7 @@
         <v>45691</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63834,7 +63834,7 @@
         <v>44481</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63907,7 +63907,7 @@
         <v>45170</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63980,7 +63980,7 @@
         <v>45497</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>45497</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64126,7 +64126,7 @@
         <v>44462</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45119</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64272,7 +64272,7 @@
         <v>45401</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64345,7 +64345,7 @@
         <v>44952</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64418,7 +64418,7 @@
         <v>45112</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45107</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>44747</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64637,7 +64637,7 @@
         <v>45526</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64710,7 +64710,7 @@
         <v>44600</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         <v>45827</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64856,7 +64856,7 @@
         <v>45569</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64929,7 +64929,7 @@
         <v>44930</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65002,7 +65002,7 @@
         <v>45033</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65075,7 +65075,7 @@
         <v>45589</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65148,7 +65148,7 @@
         <v>45572</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>45341</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>45348</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65367,7 +65367,7 @@
         <v>44740</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65445,7 +65445,7 @@
         <v>45406</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65518,7 +65518,7 @@
         <v>44998</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65591,7 +65591,7 @@
         <v>45302</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65664,7 +65664,7 @@
         <v>44869</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65737,7 +65737,7 @@
         <v>45174</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65810,7 +65810,7 @@
         <v>46153</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65883,7 +65883,7 @@
         <v>45363</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65961,7 +65961,7 @@
         <v>45363</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66039,7 +66039,7 @@
         <v>45363</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66117,7 +66117,7 @@
         <v>45364</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66190,7 +66190,7 @@
         <v>45104</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66263,7 +66263,7 @@
         <v>45281</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66336,7 +66336,7 @@
         <v>45525</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66409,7 +66409,7 @@
         <v>46153</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66482,7 +66482,7 @@
         <v>45006</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66555,7 +66555,7 @@
         <v>45202</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66628,7 +66628,7 @@
         <v>45563</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66706,7 +66706,7 @@
         <v>44447</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66779,7 +66779,7 @@
         <v>45357</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66852,7 +66852,7 @@
         <v>46153</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66925,7 +66925,7 @@
         <v>46153</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66998,7 +66998,7 @@
         <v>46153</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67071,7 +67071,7 @@
         <v>45173</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67144,7 +67144,7 @@
         <v>46154</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67222,7 +67222,7 @@
         <v>45866</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67295,7 +67295,7 @@
         <v>45639</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67368,7 +67368,7 @@
         <v>45629</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67441,7 +67441,7 @@
         <v>45314</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67514,7 +67514,7 @@
         <v>46126</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67587,7 +67587,7 @@
         <v>44448</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67665,7 +67665,7 @@
         <v>45420</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67738,7 +67738,7 @@
         <v>45195</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67811,7 +67811,7 @@
         <v>45238</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67889,7 +67889,7 @@
         <v>44880</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67962,7 +67962,7 @@
         <v>44880</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68035,7 +68035,7 @@
         <v>45400</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68113,7 +68113,7 @@
         <v>45079</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68186,7 +68186,7 @@
         <v>46160</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68259,7 +68259,7 @@
         <v>45091</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68332,7 +68332,7 @@
         <v>46161</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68405,7 +68405,7 @@
         <v>46160</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68478,7 +68478,7 @@
         <v>44602</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68551,7 +68551,7 @@
         <v>45163</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68624,7 +68624,7 @@
         <v>45761</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68697,7 +68697,7 @@
         <v>46160</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68770,7 +68770,7 @@
         <v>46064</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68843,7 +68843,7 @@
         <v>44523</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68916,7 +68916,7 @@
         <v>45930</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68989,7 +68989,7 @@
         <v>44677</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69062,7 +69062,7 @@
         <v>46160</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69135,7 +69135,7 @@
         <v>45303</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69208,7 +69208,7 @@
         <v>44592</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69281,7 +69281,7 @@
         <v>46163</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69354,7 +69354,7 @@
         <v>45475</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69427,7 +69427,7 @@
         <v>46161</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69500,7 +69500,7 @@
         <v>45211</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69573,7 +69573,7 @@
         <v>45352</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69646,7 +69646,7 @@
         <v>45538</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69719,7 +69719,7 @@
         <v>45329</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69797,7 +69797,7 @@
         <v>45314</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69870,7 +69870,7 @@
         <v>45645</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69948,7 +69948,7 @@
         <v>44815</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70021,7 +70021,7 @@
         <v>44497</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70094,7 +70094,7 @@
         <v>45930</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70172,7 +70172,7 @@
         <v>45091</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70245,7 +70245,7 @@
         <v>45022</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70318,7 +70318,7 @@
         <v>45526</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70391,7 +70391,7 @@
         <v>45114</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70464,7 +70464,7 @@
         <v>45440</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70537,7 +70537,7 @@
         <v>44587</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70610,7 +70610,7 @@
         <v>44715</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70683,7 +70683,7 @@
         <v>44813</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70756,7 +70756,7 @@
         <v>45365</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70829,7 +70829,7 @@
         <v>45385</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70902,7 +70902,7 @@
         <v>44946</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70975,7 +70975,7 @@
         <v>44805</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71048,7 +71048,7 @@
         <v>44813</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71121,7 +71121,7 @@
         <v>45398</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71194,7 +71194,7 @@
         <v>46175</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71267,7 +71267,7 @@
         <v>45307</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71340,7 +71340,7 @@
         <v>44825</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71413,7 +71413,7 @@
         <v>44917</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71486,7 +71486,7 @@
         <v>45177</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71564,7 +71564,7 @@
         <v>45174</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71642,7 +71642,7 @@
         <v>45329</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71715,7 +71715,7 @@
         <v>45245</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71788,7 +71788,7 @@
         <v>46178</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71861,7 +71861,7 @@
         <v>45737</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71934,7 +71934,7 @@
         <v>45719</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72007,7 +72007,7 @@
         <v>46178</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72080,7 +72080,7 @@
         <v>46178</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72153,7 +72153,7 @@
         <v>46178</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72226,7 +72226,7 @@
         <v>46178</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72299,7 +72299,7 @@
         <v>46178</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72372,7 +72372,7 @@
         <v>45364</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72445,7 +72445,7 @@
         <v>46178</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72518,7 +72518,7 @@
         <v>46178</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72591,7 +72591,7 @@
         <v>45089</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72664,7 +72664,7 @@
         <v>44459</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72737,7 +72737,7 @@
         <v>45660</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72810,7 +72810,7 @@
         <v>46182</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72883,7 +72883,7 @@
         <v>46182</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72956,7 +72956,7 @@
         <v>45107</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73029,7 +73029,7 @@
         <v>45184</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73102,7 +73102,7 @@
         <v>45589</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73175,7 +73175,7 @@
         <v>45589</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73248,7 +73248,7 @@
         <v>45532</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73321,7 +73321,7 @@
         <v>46182</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73394,7 +73394,7 @@
         <v>45370</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73467,7 +73467,7 @@
         <v>45406</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73540,7 +73540,7 @@
         <v>46184</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73613,7 +73613,7 @@
         <v>44595</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73686,7 +73686,7 @@
         <v>46184</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73759,7 +73759,7 @@
         <v>45104</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73832,7 +73832,7 @@
         <v>46184</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73905,7 +73905,7 @@
         <v>45071</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73978,7 +73978,7 @@
         <v>46185</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74051,7 +74051,7 @@
         <v>45216</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74124,7 +74124,7 @@
         <v>46188</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74197,7 +74197,7 @@
         <v>45303</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74270,7 +74270,7 @@
         <v>46185</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74343,7 +74343,7 @@
         <v>45678</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74416,7 +74416,7 @@
         <v>45182</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74489,7 +74489,7 @@
         <v>44495</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74562,7 +74562,7 @@
         <v>45219</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74635,7 +74635,7 @@
         <v>45030</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74708,7 +74708,7 @@
         <v>46233</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74781,7 +74781,7 @@
         <v>45544</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74854,7 +74854,7 @@
         <v>45691</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74927,7 +74927,7 @@
         <v>46190</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75000,7 +75000,7 @@
         <v>44488</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75073,7 +75073,7 @@
         <v>45631</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75146,7 +75146,7 @@
         <v>45216</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75224,7 +75224,7 @@
         <v>46234</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75297,7 +75297,7 @@
         <v>45925</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75370,7 +75370,7 @@
         <v>45359</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75443,7 +75443,7 @@
         <v>46237</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75516,7 +75516,7 @@
         <v>46234</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75589,7 +75589,7 @@
         <v>46195</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75662,7 +75662,7 @@
         <v>45376</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75735,7 +75735,7 @@
         <v>44810</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75808,7 +75808,7 @@
         <v>45209</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75881,7 +75881,7 @@
         <v>45183</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75954,7 +75954,7 @@
         <v>45595</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76027,7 +76027,7 @@
         <v>45575</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76100,7 +76100,7 @@
         <v>46196</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76173,7 +76173,7 @@
         <v>46196</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76246,7 +76246,7 @@
         <v>45062</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76319,7 +76319,7 @@
         <v>46240</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76392,7 +76392,7 @@
         <v>45231</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76465,7 +76465,7 @@
         <v>45699</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76538,7 +76538,7 @@
         <v>45737</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76611,7 +76611,7 @@
         <v>44930</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76684,7 +76684,7 @@
         <v>44971</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76757,7 +76757,7 @@
         <v>45602</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76830,7 +76830,7 @@
         <v>46197</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76903,7 +76903,7 @@
         <v>45092</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76976,7 +76976,7 @@
         <v>45674</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77049,7 +77049,7 @@
         <v>46197</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77122,7 +77122,7 @@
         <v>45478</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77195,7 +77195,7 @@
         <v>46244</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77268,7 +77268,7 @@
         <v>46202</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77341,7 +77341,7 @@
         <v>45769</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77419,7 +77419,7 @@
         <v>45164</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77492,7 +77492,7 @@
         <v>46244</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77565,7 +77565,7 @@
         <v>45309</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77638,7 +77638,7 @@
         <v>45309</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77711,7 +77711,7 @@
         <v>45182</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77789,7 +77789,7 @@
         <v>46204</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77862,7 +77862,7 @@
         <v>46246</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77935,7 +77935,7 @@
         <v>45329</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78008,7 +78008,7 @@
         <v>45222</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78081,7 +78081,7 @@
         <v>45492</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78154,7 +78154,7 @@
         <v>45323</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78227,7 +78227,7 @@
         <v>45763</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78300,7 +78300,7 @@
         <v>45384</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78373,7 +78373,7 @@
         <v>45296</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78446,7 +78446,7 @@
         <v>45763</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78519,7 +78519,7 @@
         <v>45763</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78592,7 +78592,7 @@
         <v>45763</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78665,7 +78665,7 @@
         <v>44946</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78738,7 +78738,7 @@
         <v>45462</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78811,7 +78811,7 @@
         <v>44879</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78884,7 +78884,7 @@
         <v>45719</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78957,7 +78957,7 @@
         <v>45540</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79030,7 +79030,7 @@
         <v>45134</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79103,7 +79103,7 @@
         <v>45316</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79176,7 +79176,7 @@
         <v>45414</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79249,7 +79249,7 @@
         <v>45607</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79322,7 +79322,7 @@
         <v>44818</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79395,7 +79395,7 @@
         <v>45673</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79468,7 +79468,7 @@
         <v>46245</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79541,7 +79541,7 @@
         <v>44831</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79614,7 +79614,7 @@
         <v>45001</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79692,7 +79692,7 @@
         <v>45254</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79770,7 +79770,7 @@
         <v>45090</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79843,7 +79843,7 @@
         <v>45132</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79916,7 +79916,7 @@
         <v>45335</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79989,7 +79989,7 @@
         <v>45602</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80062,7 +80062,7 @@
         <v>44963</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80135,7 +80135,7 @@
         <v>45168</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80208,7 +80208,7 @@
         <v>45400</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80281,7 +80281,7 @@
         <v>45188</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80354,7 +80354,7 @@
         <v>45670</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80427,7 +80427,7 @@
         <v>44902</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80500,7 +80500,7 @@
         <v>44564</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80578,7 +80578,7 @@
         <v>46252</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80651,7 +80651,7 @@
         <v>45189</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80729,7 +80729,7 @@
         <v>45691</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80802,7 +80802,7 @@
         <v>44916</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80875,7 +80875,7 @@
         <v>44957</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80948,7 +80948,7 @@
         <v>44502</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81021,7 +81021,7 @@
         <v>45702</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81099,7 +81099,7 @@
         <v>45134</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81172,7 +81172,7 @@
         <v>45348</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81245,7 +81245,7 @@
         <v>45439</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81318,7 +81318,7 @@
         <v>44781</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81391,7 +81391,7 @@
         <v>45783</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81464,7 +81464,7 @@
         <v>45783</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81537,7 +81537,7 @@
         <v>46255</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81610,7 +81610,7 @@
         <v>46069</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81683,7 +81683,7 @@
         <v>46259</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81756,7 +81756,7 @@
         <v>45439</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81829,7 +81829,7 @@
         <v>44592</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81902,7 +81902,7 @@
         <v>45786</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81975,7 +81975,7 @@
         <v>45601</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82048,7 +82048,7 @@
         <v>45456</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82121,7 +82121,7 @@
         <v>46213</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82194,7 +82194,7 @@
         <v>45716</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82267,7 +82267,7 @@
         <v>46247</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82345,7 +82345,7 @@
         <v>46248</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82423,7 +82423,7 @@
         <v>46168</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82496,7 +82496,7 @@
         <v>46258</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82569,7 +82569,7 @@
         <v>46259</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82642,7 +82642,7 @@
         <v>46177</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82715,7 +82715,7 @@
         <v>45792</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82788,7 +82788,7 @@
         <v>45992</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82861,7 +82861,7 @@
         <v>46265</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82934,7 +82934,7 @@
         <v>46234</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83007,7 +83007,7 @@
         <v>46178</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83080,7 +83080,7 @@
         <v>46247</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83158,7 +83158,7 @@
         <v>46269</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83231,7 +83231,7 @@
         <v>46268</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83304,7 +83304,7 @@
         <v>46258</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83377,7 +83377,7 @@
         <v>45636</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83450,7 +83450,7 @@
         <v>45580</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83523,7 +83523,7 @@
         <v>45447</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83596,7 +83596,7 @@
         <v>45170</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83669,7 +83669,7 @@
         <v>45106</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83742,7 +83742,7 @@
         <v>45467</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83815,7 +83815,7 @@
         <v>44509</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83893,7 +83893,7 @@
         <v>45664</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83966,7 +83966,7 @@
         <v>45208</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84039,7 +84039,7 @@
         <v>45406</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84112,7 +84112,7 @@
         <v>45497</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84185,7 +84185,7 @@
         <v>45497</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84258,7 +84258,7 @@
         <v>45106</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84331,7 +84331,7 @@
         <v>45646</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84404,7 +84404,7 @@
         <v>44459</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84477,7 +84477,7 @@
         <v>45646</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84550,7 +84550,7 @@
         <v>45580</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84623,7 +84623,7 @@
         <v>45646</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -84696,7 +84696,7 @@
         <v>45646</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -84769,7 +84769,7 @@
         <v>45408</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -84842,7 +84842,7 @@
         <v>45414</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84915,7 +84915,7 @@
         <v>45173</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84988,7 +84988,7 @@
         <v>45646</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -85061,7 +85061,7 @@
         <v>45715</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -85134,7 +85134,7 @@
         <v>45720</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -85207,7 +85207,7 @@
         <v>45800</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -85285,7 +85285,7 @@
         <v>45831</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -85358,7 +85358,7 @@
         <v>45785</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -85431,7 +85431,7 @@
         <v>46073</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -85504,7 +85504,7 @@
         <v>46163</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>

--- a/Översikt VETLANDA.xlsx
+++ b/Översikt VETLANDA.xlsx
@@ -601,7 +601,7 @@
         <v>45097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>46178</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>45371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44817</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>44890</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45520</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45754</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>44612</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>44840</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44908</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>46100</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45819</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46163</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45583</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>46045</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>44819</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>45763</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45477</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45814</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45048</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>45646</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45131</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>45589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>44468</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45792</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45835</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>45713</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>45840</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45860</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45673</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>45303</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>45148</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45891</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45357</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45616</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>46166</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45035</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45400</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45211</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>45310</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45106</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>45509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>45201</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>45539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>46051</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44462</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>44721</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44747</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44454</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>44592</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44740</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45597</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>44830</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>45596</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45736</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>45555</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45835</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45021</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45820</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>44748</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45904</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45645</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45839</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44824</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>45713</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45240</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44728</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45342</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>45586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>45672</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45239</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>46069</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>46071</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>44998</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44880</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>45419</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>45775</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45085</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45408</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45880</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44819</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45119</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>46141</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45009</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45261</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45378</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45104</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>44816</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45532</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>46188</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44833</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45337</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45565</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>44916</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45930</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>46248</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45352</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45643</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>45791</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>45604</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45497</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45614</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44453</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44490</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44858</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44838</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44781</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>44732</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44508</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>44889</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>44579</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>44544</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44601</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>44510</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>44468</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>44517</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>44764</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>44503</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>44819</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>44459</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>44592</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44750</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44825</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>44460</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>44488</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44638</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>44721</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>44510</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>44785</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44592</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44587</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>44782</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44815</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44453</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44504</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44580</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44691</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44880</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44460</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44453</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44545</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44750</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44462</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44624</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44446</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44477</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44595</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44608</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44454</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>44820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44460</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44816</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>44461</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>44645</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44819</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44656</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44784</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44585</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44585</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>44585</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44834</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>44740</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>44750</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44587</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>44743</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>44474</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>44600</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>44859</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>44593</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44743</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44778</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44504</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>44834</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>44482</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44509</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>44477</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44517</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>44592</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>44721</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44572</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>44841</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44888</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44587</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>44655</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44461</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>44454</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>44459</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>44515</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>44502</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44592</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>44462</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>44564</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>44781</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>44531</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44636</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>44834</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44733</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>44683</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44463</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>44602</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>44792</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>44657</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44827</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45561</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45251</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>44967</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44967</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44792</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>44592</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>45265</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>45267</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44880</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>45569</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>44902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45580</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44488</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>44903</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45674</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45175</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>44998</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45663</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45278</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45205</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45771</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45771</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45057</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45259</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>44477</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>45351</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45602</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>44582</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>44936</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>45264</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44831</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45091</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45188</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45307</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45575</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>44530</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
         <v>45350</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>45071</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45135</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>45229</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45055</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44600</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44851</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45406</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>44762</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>44710</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44986</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45384</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45434</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45439</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>44747</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45031</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45097</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45097</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45645</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45335</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>45104</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45300</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45709</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>45645</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>45099</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45309</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45309</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45470</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44949</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45097</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45272</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45309</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>44487</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45363</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45118</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45336</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45161</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45162</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45414</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45226</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>45188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44916</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44916</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45701</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45082</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45741</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45461</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45163</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45741</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45728</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45188</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>44655</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45259</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45580</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45610</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45743</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45737</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45737</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45341</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45742</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45191</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>44952</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>45733</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45733</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45209</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44888</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45803</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45743</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>45442</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>45708</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>45113</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>45616</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45839</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45359</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45754</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45754</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45351</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45628</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>44972</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45097</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45201</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45805</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44770</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45572</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>44916</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45884</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45434</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45190</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45811</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44592</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45448</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45166</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45615</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>45505</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45580</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>45625</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45362</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>46003</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44462</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45812</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45816</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>46029</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44977</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>45888</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>45888</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45541</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45677</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45545</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45889</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45786</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45819</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45888</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>45742</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45104</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45889</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45888</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45888</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45645</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45888</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45645</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>45754</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45826</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45889</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45742</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>45135</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45770</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>45819</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45135</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45135</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>45819</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45819</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>44641</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44482</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>45042</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45329</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>45586</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>45329</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45117</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45839</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>45623</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>44888</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45099</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45610</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45742</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44984</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>46031</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45898</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>45228</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45819</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45737</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45587</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45441</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45902</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>46031</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45274</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44693</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45595</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>46030</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45330</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>45202</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45702</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45376</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>46030</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45363</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>44916</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45911</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45911</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>44531</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>45737</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45365</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45414</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45838</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>46031</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45839</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45107</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37439,7 +37439,7 @@
         <v>45251</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>45319</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45922</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45840</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>44515</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>44984</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45840</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45232</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45462</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45845</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45925</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>44984</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38320,7 +38320,7 @@
         <v>44984</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>45357</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>45729</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>45748</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>45747</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>45048</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>45625</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>45715</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>45925</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>45715</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>44834</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>45581</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45847</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>44945</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45006</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45069</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45763</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>45931</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45484</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45852</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>45015</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>45310</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>45351</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>45170</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45672</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>45936</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>45163</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45936</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44549</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45322</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>45097</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45005</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>44564</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>45684</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45330</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>44946</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>45866</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>45107</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45288</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45733</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45099</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41323,7 +41323,7 @@
         <v>45113</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>45944</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>44460</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45352</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>45946</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>44837</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41761,7 +41761,7 @@
         <v>45875</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>45950</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45351</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45875</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45875</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45953</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>44484</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>45953</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45748</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>45748</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>46044</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>46045</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42647,7 +42647,7 @@
         <v>44965</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>46048</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>46048</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>46048</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>46049</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>46048</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45882</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45882</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45884</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>46055</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>44970</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45133</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         <v>45357</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45133</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45231</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>44545</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>45681</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>45152</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>44503</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45230</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>44480</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>44741</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>45272</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45084</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44600</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45331</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45331</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>45222</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>44970</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>45671</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45435</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>45230</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45204</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45455</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>45561</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>46062</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>46063</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45282</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45245</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>46062</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>46063</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>46063</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>46063</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>45631</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>45247</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45259</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>45370</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45322</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45974</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>45975</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45035</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>45645</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>45645</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45076</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>45006</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>44580</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45089</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>45981</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>44459</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>45981</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45615</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45981</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>45538</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>45298</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47344,7 +47344,7 @@
         <v>45982</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45981</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>46077</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47563,7 +47563,7 @@
         <v>45372</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45076</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>46077</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>44473</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47855,7 +47855,7 @@
         <v>45170</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45401</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44607</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>44837</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>44511</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45089</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45443</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48366,7 +48366,7 @@
         <v>45992</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45240</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>45992</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45168</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48658,7 +48658,7 @@
         <v>45992</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48731,7 +48731,7 @@
         <v>45321</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48804,7 +48804,7 @@
         <v>45992</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>44470</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48950,7 +48950,7 @@
         <v>45163</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49023,7 +49023,7 @@
         <v>44510</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>45999</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45999</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>45211</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45414</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         <v>44894</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49461,7 +49461,7 @@
         <v>45519</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45314</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>45433</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45097</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>46084</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45448</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>46084</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>46001</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>45645</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         <v>45645</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>46084</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45644</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>46003</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>45649</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>45114</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>44858</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>46009</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>45545</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>46007</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50863,7 +50863,7 @@
         <v>46007</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50936,7 +50936,7 @@
         <v>46009</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45250</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51082,7 +51082,7 @@
         <v>45224</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>45999</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>46009</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>46009</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>46010</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45645</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>46010</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45763</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>46087</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>45672</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>45264</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45827</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>46091</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52041,7 +52041,7 @@
         <v>45525</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52114,7 +52114,7 @@
         <v>44965</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>44926</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>44926</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45401</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>46092</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>46092</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>45392</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45394</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>46002</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>44602</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>46097</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>45007</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>46098</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>45568</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45297</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53214,7 +53214,7 @@
         <v>45236</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45625</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53360,7 +53360,7 @@
         <v>45105</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>46099</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>44859</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>46100</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>46104</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53725,7 +53725,7 @@
         <v>46104</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53798,7 +53798,7 @@
         <v>46104</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45674</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>44481</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54017,7 +54017,7 @@
         <v>46107</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54090,7 +54090,7 @@
         <v>46107</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54163,7 +54163,7 @@
         <v>44655</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>44970</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>45329</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54382,7 +54382,7 @@
         <v>46107</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54455,7 +54455,7 @@
         <v>44847</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54528,7 +54528,7 @@
         <v>46111</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54601,7 +54601,7 @@
         <v>45180</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45173</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45173</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54820,7 +54820,7 @@
         <v>46111</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45345</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54966,7 +54966,7 @@
         <v>45526</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55039,7 +55039,7 @@
         <v>45170</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>45170</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45303</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>45104</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>46121</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55404,7 +55404,7 @@
         <v>46122</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>46121</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>45113</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>44462</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45446</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45438</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55842,7 +55842,7 @@
         <v>46126</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>46128</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55988,7 +55988,7 @@
         <v>46128</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56061,7 +56061,7 @@
         <v>46128</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>46128</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56207,7 +56207,7 @@
         <v>46127</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>45182</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56358,7 +56358,7 @@
         <v>45182</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>46128</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>44607</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>46133</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56650,7 +56650,7 @@
         <v>46133</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>45669</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>45315</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>45462</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45449</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57015,7 +57015,7 @@
         <v>44463</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57088,7 +57088,7 @@
         <v>45327</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57161,7 +57161,7 @@
         <v>45164</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45330</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45903</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>44995</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57453,7 +57453,7 @@
         <v>45692</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>45839</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57599,7 +57599,7 @@
         <v>45699</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57672,7 +57672,7 @@
         <v>45827</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57745,7 +57745,7 @@
         <v>46037</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57818,7 +57818,7 @@
         <v>45944</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57891,7 +57891,7 @@
         <v>45112</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57964,7 +57964,7 @@
         <v>45106</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58037,7 +58037,7 @@
         <v>45574</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45616</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58188,7 +58188,7 @@
         <v>45891</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45313</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>45799</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45510</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45306</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45219</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>45274</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58704,7 +58704,7 @@
         <v>45250</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58777,7 +58777,7 @@
         <v>45931</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>44587</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58923,7 +58923,7 @@
         <v>44783</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>44510</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>45895</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>45883</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>44830</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45544</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59361,7 +59361,7 @@
         <v>45133</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59434,7 +59434,7 @@
         <v>45408</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59507,7 +59507,7 @@
         <v>44834</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59580,7 +59580,7 @@
         <v>45366</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59653,7 +59653,7 @@
         <v>44815</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59726,7 +59726,7 @@
         <v>45069</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>45440</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59872,7 +59872,7 @@
         <v>45902</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59945,7 +59945,7 @@
         <v>45701</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60023,7 +60023,7 @@
         <v>46112</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60101,7 +60101,7 @@
         <v>45965</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60174,7 +60174,7 @@
         <v>45302</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60247,7 +60247,7 @@
         <v>45615</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>45525</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60393,7 +60393,7 @@
         <v>45113</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45785</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60539,7 +60539,7 @@
         <v>45912</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60612,7 +60612,7 @@
         <v>44683</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60685,7 +60685,7 @@
         <v>45840</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60758,7 +60758,7 @@
         <v>45866</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>45546</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60904,7 +60904,7 @@
         <v>45925</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>45971</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>44839</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>44970</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45222</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>46006</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>45183</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>45763</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61488,7 +61488,7 @@
         <v>44965</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45000</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61634,7 +61634,7 @@
         <v>45183</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45706</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61780,7 +61780,7 @@
         <v>45693</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61853,7 +61853,7 @@
         <v>45889</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61926,7 +61926,7 @@
         <v>45785</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61999,7 +61999,7 @@
         <v>44839</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         <v>44753</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>45841</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>45135</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>46136</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45608</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62437,7 +62437,7 @@
         <v>45873</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>45971</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45610</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>46122</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45153</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>45755</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>45670</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62948,7 +62948,7 @@
         <v>45825</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45348</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63094,7 +63094,7 @@
         <v>45839</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63167,7 +63167,7 @@
         <v>44802</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63245,7 +63245,7 @@
         <v>44538</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63318,7 +63318,7 @@
         <v>45446</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63391,7 +63391,7 @@
         <v>44785</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>46052</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63537,7 +63537,7 @@
         <v>45883</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63610,7 +63610,7 @@
         <v>44929</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63683,7 +63683,7 @@
         <v>44743</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63756,7 +63756,7 @@
         <v>45691</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63834,7 +63834,7 @@
         <v>44481</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63907,7 +63907,7 @@
         <v>45170</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63980,7 +63980,7 @@
         <v>45497</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>45497</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64126,7 +64126,7 @@
         <v>44462</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45119</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64272,7 +64272,7 @@
         <v>45401</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64345,7 +64345,7 @@
         <v>44952</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64418,7 +64418,7 @@
         <v>45112</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45107</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>44747</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64637,7 +64637,7 @@
         <v>45526</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64710,7 +64710,7 @@
         <v>44600</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         <v>45827</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64856,7 +64856,7 @@
         <v>45569</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64929,7 +64929,7 @@
         <v>44930</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65002,7 +65002,7 @@
         <v>45033</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65075,7 +65075,7 @@
         <v>45589</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65148,7 +65148,7 @@
         <v>45572</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>45341</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>45348</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65367,7 +65367,7 @@
         <v>44740</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65445,7 +65445,7 @@
         <v>45406</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65518,7 +65518,7 @@
         <v>44998</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65591,7 +65591,7 @@
         <v>45302</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65664,7 +65664,7 @@
         <v>44869</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65737,7 +65737,7 @@
         <v>45174</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65810,7 +65810,7 @@
         <v>46153</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65883,7 +65883,7 @@
         <v>45363</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65961,7 +65961,7 @@
         <v>45363</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66039,7 +66039,7 @@
         <v>45363</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66117,7 +66117,7 @@
         <v>45364</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66190,7 +66190,7 @@
         <v>45104</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66263,7 +66263,7 @@
         <v>45281</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66336,7 +66336,7 @@
         <v>45525</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66409,7 +66409,7 @@
         <v>46153</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66482,7 +66482,7 @@
         <v>45006</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66555,7 +66555,7 @@
         <v>45202</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66628,7 +66628,7 @@
         <v>45563</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66706,7 +66706,7 @@
         <v>44447</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66779,7 +66779,7 @@
         <v>45357</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66852,7 +66852,7 @@
         <v>46153</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66925,7 +66925,7 @@
         <v>46153</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66998,7 +66998,7 @@
         <v>46153</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67071,7 +67071,7 @@
         <v>45173</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67144,7 +67144,7 @@
         <v>46154</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67222,7 +67222,7 @@
         <v>45866</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67295,7 +67295,7 @@
         <v>45639</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67368,7 +67368,7 @@
         <v>45629</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67441,7 +67441,7 @@
         <v>45314</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67514,7 +67514,7 @@
         <v>46126</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67587,7 +67587,7 @@
         <v>44448</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67665,7 +67665,7 @@
         <v>45420</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67738,7 +67738,7 @@
         <v>45195</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67811,7 +67811,7 @@
         <v>45238</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67889,7 +67889,7 @@
         <v>44880</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67962,7 +67962,7 @@
         <v>44880</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68035,7 +68035,7 @@
         <v>45400</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68113,7 +68113,7 @@
         <v>45079</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68186,7 +68186,7 @@
         <v>46160</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68259,7 +68259,7 @@
         <v>45091</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68332,7 +68332,7 @@
         <v>46161</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68405,7 +68405,7 @@
         <v>46160</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68478,7 +68478,7 @@
         <v>44602</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68551,7 +68551,7 @@
         <v>45163</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68624,7 +68624,7 @@
         <v>45761</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68697,7 +68697,7 @@
         <v>46160</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68770,7 +68770,7 @@
         <v>46064</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68843,7 +68843,7 @@
         <v>44523</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68916,7 +68916,7 @@
         <v>45930</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68989,7 +68989,7 @@
         <v>44677</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69062,7 +69062,7 @@
         <v>46160</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69135,7 +69135,7 @@
         <v>45303</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69208,7 +69208,7 @@
         <v>44592</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69281,7 +69281,7 @@
         <v>46163</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69354,7 +69354,7 @@
         <v>45475</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69427,7 +69427,7 @@
         <v>46161</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69500,7 +69500,7 @@
         <v>45211</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69573,7 +69573,7 @@
         <v>45352</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69646,7 +69646,7 @@
         <v>45538</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69719,7 +69719,7 @@
         <v>45329</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69797,7 +69797,7 @@
         <v>45314</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69870,7 +69870,7 @@
         <v>45645</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69948,7 +69948,7 @@
         <v>44815</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70021,7 +70021,7 @@
         <v>44497</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70094,7 +70094,7 @@
         <v>45930</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70172,7 +70172,7 @@
         <v>45091</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70245,7 +70245,7 @@
         <v>45022</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70318,7 +70318,7 @@
         <v>45526</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70391,7 +70391,7 @@
         <v>45114</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70464,7 +70464,7 @@
         <v>45440</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70537,7 +70537,7 @@
         <v>44587</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70610,7 +70610,7 @@
         <v>44715</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70683,7 +70683,7 @@
         <v>44813</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70756,7 +70756,7 @@
         <v>45365</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70829,7 +70829,7 @@
         <v>45385</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70902,7 +70902,7 @@
         <v>44946</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70975,7 +70975,7 @@
         <v>44805</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71048,7 +71048,7 @@
         <v>44813</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71121,7 +71121,7 @@
         <v>45398</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71194,7 +71194,7 @@
         <v>46175</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71267,7 +71267,7 @@
         <v>45307</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71340,7 +71340,7 @@
         <v>44825</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71413,7 +71413,7 @@
         <v>44917</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71486,7 +71486,7 @@
         <v>45177</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71564,7 +71564,7 @@
         <v>45174</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71642,7 +71642,7 @@
         <v>45329</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71715,7 +71715,7 @@
         <v>45245</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71788,7 +71788,7 @@
         <v>46178</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71861,7 +71861,7 @@
         <v>45737</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71934,7 +71934,7 @@
         <v>45719</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72007,7 +72007,7 @@
         <v>46178</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72080,7 +72080,7 @@
         <v>46178</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72153,7 +72153,7 @@
         <v>46178</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72226,7 +72226,7 @@
         <v>46178</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72299,7 +72299,7 @@
         <v>46178</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72372,7 +72372,7 @@
         <v>45364</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72445,7 +72445,7 @@
         <v>46178</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72518,7 +72518,7 @@
         <v>46178</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72591,7 +72591,7 @@
         <v>45089</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72664,7 +72664,7 @@
         <v>44459</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72737,7 +72737,7 @@
         <v>45660</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72810,7 +72810,7 @@
         <v>46182</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72883,7 +72883,7 @@
         <v>46182</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72956,7 +72956,7 @@
         <v>45107</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73029,7 +73029,7 @@
         <v>45184</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73102,7 +73102,7 @@
         <v>45589</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73175,7 +73175,7 @@
         <v>45589</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73248,7 +73248,7 @@
         <v>45532</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73321,7 +73321,7 @@
         <v>46182</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73394,7 +73394,7 @@
         <v>45370</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73467,7 +73467,7 @@
         <v>45406</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73540,7 +73540,7 @@
         <v>46184</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73613,7 +73613,7 @@
         <v>44595</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73686,7 +73686,7 @@
         <v>46184</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73759,7 +73759,7 @@
         <v>45104</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73832,7 +73832,7 @@
         <v>46184</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73905,7 +73905,7 @@
         <v>45071</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73978,7 +73978,7 @@
         <v>46185</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74051,7 +74051,7 @@
         <v>45216</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74124,7 +74124,7 @@
         <v>46188</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74197,7 +74197,7 @@
         <v>45303</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74270,7 +74270,7 @@
         <v>46185</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74343,7 +74343,7 @@
         <v>45678</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74416,7 +74416,7 @@
         <v>45182</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74489,7 +74489,7 @@
         <v>44495</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74562,7 +74562,7 @@
         <v>45219</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74635,7 +74635,7 @@
         <v>45030</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74708,7 +74708,7 @@
         <v>46233</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74781,7 +74781,7 @@
         <v>45544</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74854,7 +74854,7 @@
         <v>45691</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74927,7 +74927,7 @@
         <v>46190</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75000,7 +75000,7 @@
         <v>44488</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75073,7 +75073,7 @@
         <v>45631</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75146,7 +75146,7 @@
         <v>45216</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75224,7 +75224,7 @@
         <v>46234</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75297,7 +75297,7 @@
         <v>45925</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75370,7 +75370,7 @@
         <v>45359</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75443,7 +75443,7 @@
         <v>46237</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75516,7 +75516,7 @@
         <v>46234</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75589,7 +75589,7 @@
         <v>46195</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75662,7 +75662,7 @@
         <v>45376</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75735,7 +75735,7 @@
         <v>44810</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75808,7 +75808,7 @@
         <v>45209</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75881,7 +75881,7 @@
         <v>45183</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75954,7 +75954,7 @@
         <v>45595</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76027,7 +76027,7 @@
         <v>45575</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76100,7 +76100,7 @@
         <v>46196</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76173,7 +76173,7 @@
         <v>46196</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76246,7 +76246,7 @@
         <v>45062</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76319,7 +76319,7 @@
         <v>46240</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76392,7 +76392,7 @@
         <v>45231</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76465,7 +76465,7 @@
         <v>45699</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76538,7 +76538,7 @@
         <v>45737</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76611,7 +76611,7 @@
         <v>44930</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76684,7 +76684,7 @@
         <v>44971</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76757,7 +76757,7 @@
         <v>45602</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76830,7 +76830,7 @@
         <v>46197</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76903,7 +76903,7 @@
         <v>45092</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76976,7 +76976,7 @@
         <v>45674</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77049,7 +77049,7 @@
         <v>46197</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77122,7 +77122,7 @@
         <v>45478</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77195,7 +77195,7 @@
         <v>46244</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77268,7 +77268,7 @@
         <v>46202</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77341,7 +77341,7 @@
         <v>45769</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77419,7 +77419,7 @@
         <v>45164</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77492,7 +77492,7 @@
         <v>46244</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77565,7 +77565,7 @@
         <v>45309</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77638,7 +77638,7 @@
         <v>45309</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77711,7 +77711,7 @@
         <v>45182</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77789,7 +77789,7 @@
         <v>46204</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77862,7 +77862,7 @@
         <v>46246</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77935,7 +77935,7 @@
         <v>45329</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78008,7 +78008,7 @@
         <v>45222</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78081,7 +78081,7 @@
         <v>45492</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78154,7 +78154,7 @@
         <v>45323</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78227,7 +78227,7 @@
         <v>45763</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78300,7 +78300,7 @@
         <v>45384</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78373,7 +78373,7 @@
         <v>45296</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78446,7 +78446,7 @@
         <v>45763</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78519,7 +78519,7 @@
         <v>45763</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78592,7 +78592,7 @@
         <v>45763</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78665,7 +78665,7 @@
         <v>44946</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78738,7 +78738,7 @@
         <v>45462</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78811,7 +78811,7 @@
         <v>44879</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78884,7 +78884,7 @@
         <v>45719</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78957,7 +78957,7 @@
         <v>45540</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79030,7 +79030,7 @@
         <v>45134</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79103,7 +79103,7 @@
         <v>45316</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79176,7 +79176,7 @@
         <v>45414</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79249,7 +79249,7 @@
         <v>45607</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79322,7 +79322,7 @@
         <v>44818</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79395,7 +79395,7 @@
         <v>45673</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79468,7 +79468,7 @@
         <v>46245</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79541,7 +79541,7 @@
         <v>44831</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79614,7 +79614,7 @@
         <v>45001</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79692,7 +79692,7 @@
         <v>45254</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79770,7 +79770,7 @@
         <v>45090</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79843,7 +79843,7 @@
         <v>45132</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79916,7 +79916,7 @@
         <v>45335</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79989,7 +79989,7 @@
         <v>45602</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80062,7 +80062,7 @@
         <v>44963</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80135,7 +80135,7 @@
         <v>45168</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80208,7 +80208,7 @@
         <v>45400</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80281,7 +80281,7 @@
         <v>45188</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80354,7 +80354,7 @@
         <v>45670</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80427,7 +80427,7 @@
         <v>44902</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80500,7 +80500,7 @@
         <v>44564</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80578,7 +80578,7 @@
         <v>46252</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80651,7 +80651,7 @@
         <v>45189</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80729,7 +80729,7 @@
         <v>45691</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80802,7 +80802,7 @@
         <v>44916</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80875,7 +80875,7 @@
         <v>44957</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80948,7 +80948,7 @@
         <v>44502</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81021,7 +81021,7 @@
         <v>45702</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81099,7 +81099,7 @@
         <v>45134</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81172,7 +81172,7 @@
         <v>45348</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81245,7 +81245,7 @@
         <v>45439</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81318,7 +81318,7 @@
         <v>44781</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81391,7 +81391,7 @@
         <v>45783</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81464,7 +81464,7 @@
         <v>45783</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81537,7 +81537,7 @@
         <v>46255</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81610,7 +81610,7 @@
         <v>46069</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81683,7 +81683,7 @@
         <v>46259</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81756,7 +81756,7 @@
         <v>45439</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81829,7 +81829,7 @@
         <v>44592</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81902,7 +81902,7 @@
         <v>45786</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81975,7 +81975,7 @@
         <v>45601</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82048,7 +82048,7 @@
         <v>45456</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82121,7 +82121,7 @@
         <v>46213</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82194,7 +82194,7 @@
         <v>45716</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82267,7 +82267,7 @@
         <v>46247</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82345,7 +82345,7 @@
         <v>46248</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82423,7 +82423,7 @@
         <v>46168</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82496,7 +82496,7 @@
         <v>46258</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82569,7 +82569,7 @@
         <v>46259</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82642,7 +82642,7 @@
         <v>46177</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82715,7 +82715,7 @@
         <v>45792</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82788,7 +82788,7 @@
         <v>45992</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82861,7 +82861,7 @@
         <v>46265</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82934,7 +82934,7 @@
         <v>46234</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83007,7 +83007,7 @@
         <v>46178</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83080,7 +83080,7 @@
         <v>46247</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83158,7 +83158,7 @@
         <v>46269</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83231,7 +83231,7 @@
         <v>46268</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83304,7 +83304,7 @@
         <v>46258</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83377,7 +83377,7 @@
         <v>45636</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83450,7 +83450,7 @@
         <v>45580</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83523,7 +83523,7 @@
         <v>45447</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83596,7 +83596,7 @@
         <v>45170</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83669,7 +83669,7 @@
         <v>45106</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83742,7 +83742,7 @@
         <v>45467</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83815,7 +83815,7 @@
         <v>44509</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83893,7 +83893,7 @@
         <v>45664</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83966,7 +83966,7 @@
         <v>45208</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84039,7 +84039,7 @@
         <v>45406</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84112,7 +84112,7 @@
         <v>45497</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84185,7 +84185,7 @@
         <v>45497</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84258,7 +84258,7 @@
         <v>45106</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84331,7 +84331,7 @@
         <v>45646</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84404,7 +84404,7 @@
         <v>44459</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84477,7 +84477,7 @@
         <v>45646</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84550,7 +84550,7 @@
         <v>45580</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84623,7 +84623,7 @@
         <v>45646</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -84696,7 +84696,7 @@
         <v>45646</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -84769,7 +84769,7 @@
         <v>45408</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -84842,7 +84842,7 @@
         <v>45414</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84915,7 +84915,7 @@
         <v>45173</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84988,7 +84988,7 @@
         <v>45646</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -85061,7 +85061,7 @@
         <v>45715</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -85134,7 +85134,7 @@
         <v>45720</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -85207,7 +85207,7 @@
         <v>45800</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -85285,7 +85285,7 @@
         <v>45831</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -85358,7 +85358,7 @@
         <v>45785</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -85431,7 +85431,7 @@
         <v>46073</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -85504,7 +85504,7 @@
         <v>46163</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
